--- a/resultados_barrido.xlsx
+++ b/resultados_barrido.xlsx
@@ -505,22 +505,22 @@
         <v>26.2</v>
       </c>
       <c r="G2" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="H2" t="n">
-        <v>279642</v>
+        <v>279776</v>
       </c>
       <c r="I2" t="n">
-        <v>56.4</v>
+        <v>56.44</v>
       </c>
       <c r="J2" t="n">
         <v>0.042</v>
       </c>
       <c r="K2" t="n">
-        <v>2526</v>
+        <v>2514</v>
       </c>
       <c r="L2" t="n">
-        <v>4320</v>
+        <v>4327</v>
       </c>
       <c r="M2" t="inlineStr"/>
     </row>
@@ -546,22 +546,22 @@
         <v>17.9</v>
       </c>
       <c r="G3" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="H3" t="n">
-        <v>233227</v>
+        <v>233311</v>
       </c>
       <c r="I3" t="n">
-        <v>46.56</v>
+        <v>46.61</v>
       </c>
       <c r="J3" t="n">
-        <v>0.053</v>
+        <v>0.052</v>
       </c>
       <c r="K3" t="n">
-        <v>1969</v>
+        <v>1955</v>
       </c>
       <c r="L3" t="n">
-        <v>7035</v>
+        <v>7044</v>
       </c>
       <c r="M3" t="inlineStr"/>
     </row>
@@ -587,22 +587,22 @@
         <v>12.3</v>
       </c>
       <c r="G4" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="H4" t="n">
-        <v>189757</v>
+        <v>189882</v>
       </c>
       <c r="I4" t="n">
-        <v>37</v>
+        <v>37.03</v>
       </c>
       <c r="J4" t="n">
-        <v>0.063</v>
+        <v>0.062</v>
       </c>
       <c r="K4" t="n">
-        <v>1490</v>
+        <v>1483</v>
       </c>
       <c r="L4" t="n">
-        <v>9659</v>
+        <v>9670</v>
       </c>
       <c r="M4" t="inlineStr"/>
     </row>
@@ -625,25 +625,25 @@
         <v>25</v>
       </c>
       <c r="F5" t="n">
-        <v>17.7</v>
+        <v>17.6</v>
       </c>
       <c r="G5" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="H5" t="n">
-        <v>232754</v>
+        <v>232743</v>
       </c>
       <c r="I5" t="n">
-        <v>46.08</v>
+        <v>46.11</v>
       </c>
       <c r="J5" t="n">
-        <v>0.055</v>
+        <v>0.052</v>
       </c>
       <c r="K5" t="n">
-        <v>2106</v>
+        <v>2090</v>
       </c>
       <c r="L5" t="n">
-        <v>6054</v>
+        <v>6065</v>
       </c>
       <c r="M5" t="inlineStr"/>
     </row>
@@ -669,22 +669,22 @@
         <v>12.2</v>
       </c>
       <c r="G6" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="H6" t="n">
-        <v>188462</v>
+        <v>188518</v>
       </c>
       <c r="I6" t="n">
-        <v>36.74</v>
+        <v>36.75</v>
       </c>
       <c r="J6" t="n">
-        <v>0.063</v>
+        <v>0.062</v>
       </c>
       <c r="K6" t="n">
-        <v>1565</v>
+        <v>1557</v>
       </c>
       <c r="L6" t="n">
-        <v>8614</v>
+        <v>8630</v>
       </c>
       <c r="M6" t="inlineStr"/>
     </row>
@@ -713,19 +713,19 @@
         <v>0.1</v>
       </c>
       <c r="H7" t="n">
-        <v>148155</v>
+        <v>148190</v>
       </c>
       <c r="I7" t="n">
-        <v>27.8</v>
+        <v>27.83</v>
       </c>
       <c r="J7" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="K7" t="n">
-        <v>1128</v>
+        <v>1119</v>
       </c>
       <c r="L7" t="n">
-        <v>11038</v>
+        <v>11057</v>
       </c>
       <c r="M7" t="inlineStr"/>
     </row>
@@ -751,22 +751,22 @@
         <v>12.1</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="H8" t="n">
-        <v>188240</v>
+        <v>188351</v>
       </c>
       <c r="I8" t="n">
-        <v>36.23</v>
+        <v>36.26</v>
       </c>
       <c r="J8" t="n">
-        <v>0.065</v>
+        <v>0.063</v>
       </c>
       <c r="K8" t="n">
-        <v>1711</v>
+        <v>1704</v>
       </c>
       <c r="L8" t="n">
-        <v>7794</v>
+        <v>7799</v>
       </c>
       <c r="M8" t="inlineStr"/>
     </row>
@@ -795,19 +795,19 @@
         <v>0.1</v>
       </c>
       <c r="H9" t="n">
-        <v>146920</v>
+        <v>146968</v>
       </c>
       <c r="I9" t="n">
-        <v>27.53</v>
+        <v>27.57</v>
       </c>
       <c r="J9" t="n">
-        <v>0.073</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="K9" t="n">
-        <v>1201</v>
+        <v>1192</v>
       </c>
       <c r="L9" t="n">
-        <v>10150</v>
+        <v>10158</v>
       </c>
       <c r="M9" t="inlineStr"/>
     </row>
@@ -836,19 +836,19 @@
         <v>0.1</v>
       </c>
       <c r="H10" t="n">
-        <v>110597</v>
+        <v>110625</v>
       </c>
       <c r="I10" t="n">
-        <v>19.46</v>
+        <v>19.47</v>
       </c>
       <c r="J10" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.083</v>
       </c>
       <c r="K10" t="n">
-        <v>806</v>
+        <v>801</v>
       </c>
       <c r="L10" t="n">
-        <v>12336</v>
+        <v>12351</v>
       </c>
       <c r="M10" t="inlineStr"/>
     </row>
@@ -871,25 +871,25 @@
         <v>35</v>
       </c>
       <c r="F11" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G11" t="n">
         <v>0.1</v>
       </c>
       <c r="H11" t="n">
-        <v>147034</v>
+        <v>147041</v>
       </c>
       <c r="I11" t="n">
-        <v>27.11</v>
+        <v>27.13</v>
       </c>
       <c r="J11" t="n">
-        <v>0.074</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="K11" t="n">
-        <v>1346</v>
+        <v>1337</v>
       </c>
       <c r="L11" t="n">
-        <v>9412</v>
+        <v>9422</v>
       </c>
       <c r="M11" t="inlineStr"/>
     </row>
@@ -918,19 +918,19 @@
         <v>0.1</v>
       </c>
       <c r="H12" t="n">
-        <v>109465</v>
+        <v>109484</v>
       </c>
       <c r="I12" t="n">
-        <v>19.27</v>
+        <v>19.28</v>
       </c>
       <c r="J12" t="n">
-        <v>0.08400000000000001</v>
+        <v>0.083</v>
       </c>
       <c r="K12" t="n">
-        <v>869</v>
+        <v>864</v>
       </c>
       <c r="L12" t="n">
-        <v>11532</v>
+        <v>11548</v>
       </c>
       <c r="M12" t="inlineStr"/>
     </row>
@@ -956,22 +956,22 @@
         <v>3.7</v>
       </c>
       <c r="G13" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>78554</v>
+        <v>78529</v>
       </c>
       <c r="I13" t="n">
-        <v>12.41</v>
+        <v>12.42</v>
       </c>
       <c r="J13" t="n">
-        <v>0.094</v>
+        <v>0.092</v>
       </c>
       <c r="K13" t="n">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="L13" t="n">
-        <v>13381</v>
+        <v>13396</v>
       </c>
       <c r="M13" t="inlineStr"/>
     </row>
@@ -1000,19 +1000,19 @@
         <v>0.1</v>
       </c>
       <c r="H14" t="n">
-        <v>109927</v>
+        <v>109923</v>
       </c>
       <c r="I14" t="n">
         <v>18.89</v>
       </c>
       <c r="J14" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>1016</v>
+        <v>1011</v>
       </c>
       <c r="L14" t="n">
-        <v>10873</v>
+        <v>10885</v>
       </c>
       <c r="M14" t="inlineStr"/>
     </row>
@@ -1038,22 +1038,22 @@
         <v>3.6</v>
       </c>
       <c r="G15" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>77478</v>
+        <v>77455</v>
       </c>
       <c r="I15" t="n">
-        <v>12.27</v>
+        <v>12.28</v>
       </c>
       <c r="J15" t="n">
-        <v>0.094</v>
+        <v>0.092</v>
       </c>
       <c r="K15" t="n">
-        <v>576</v>
+        <v>571</v>
       </c>
       <c r="L15" t="n">
-        <v>12656</v>
+        <v>12667</v>
       </c>
       <c r="M15" t="inlineStr"/>
     </row>
@@ -1082,19 +1082,19 @@
         <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>53399</v>
+        <v>53479</v>
       </c>
       <c r="I16" t="n">
-        <v>6.92</v>
+        <v>6.93</v>
       </c>
       <c r="J16" t="n">
-        <v>0.101</v>
+        <v>0.099</v>
       </c>
       <c r="K16" t="n">
         <v>297</v>
       </c>
       <c r="L16" t="n">
-        <v>14092</v>
+        <v>14103</v>
       </c>
       <c r="M16" t="inlineStr"/>
     </row>
@@ -1123,19 +1123,19 @@
         <v>0.1</v>
       </c>
       <c r="H17" t="n">
-        <v>190169</v>
+        <v>190210</v>
       </c>
       <c r="I17" t="n">
-        <v>36.1</v>
+        <v>36.12</v>
       </c>
       <c r="J17" t="n">
-        <v>0.067</v>
+        <v>0.064</v>
       </c>
       <c r="K17" t="n">
-        <v>1921</v>
+        <v>1912</v>
       </c>
       <c r="L17" t="n">
-        <v>3310</v>
+        <v>3313</v>
       </c>
       <c r="M17" t="inlineStr"/>
     </row>
@@ -1164,19 +1164,19 @@
         <v>0.1</v>
       </c>
       <c r="H18" t="n">
-        <v>146945</v>
+        <v>147004</v>
       </c>
       <c r="I18" t="n">
-        <v>27.48</v>
+        <v>27.53</v>
       </c>
       <c r="J18" t="n">
-        <v>0.075</v>
+        <v>0.073</v>
       </c>
       <c r="K18" t="n">
-        <v>1327</v>
+        <v>1315</v>
       </c>
       <c r="L18" t="n">
-        <v>5715</v>
+        <v>5713</v>
       </c>
       <c r="M18" t="inlineStr"/>
     </row>
@@ -1205,19 +1205,19 @@
         <v>0.1</v>
       </c>
       <c r="H19" t="n">
-        <v>109457</v>
+        <v>109515</v>
       </c>
       <c r="I19" t="n">
-        <v>19.48</v>
+        <v>19.49</v>
       </c>
       <c r="J19" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.083</v>
       </c>
       <c r="K19" t="n">
-        <v>876</v>
+        <v>872</v>
       </c>
       <c r="L19" t="n">
-        <v>7916</v>
+        <v>7927</v>
       </c>
       <c r="M19" t="inlineStr"/>
     </row>
@@ -1246,19 +1246,19 @@
         <v>0.1</v>
       </c>
       <c r="H20" t="n">
-        <v>146621</v>
+        <v>146684</v>
       </c>
       <c r="I20" t="n">
-        <v>27.07</v>
+        <v>27.1</v>
       </c>
       <c r="J20" t="n">
-        <v>0.075</v>
+        <v>0.074</v>
       </c>
       <c r="K20" t="n">
-        <v>1459</v>
+        <v>1450</v>
       </c>
       <c r="L20" t="n">
-        <v>4317</v>
+        <v>4323</v>
       </c>
       <c r="M20" t="inlineStr"/>
     </row>
@@ -1287,19 +1287,19 @@
         <v>0.1</v>
       </c>
       <c r="H21" t="n">
-        <v>108103</v>
+        <v>108147</v>
       </c>
       <c r="I21" t="n">
-        <v>19.29</v>
+        <v>19.3</v>
       </c>
       <c r="J21" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.083</v>
       </c>
       <c r="K21" t="n">
-        <v>936</v>
+        <v>932</v>
       </c>
       <c r="L21" t="n">
-        <v>6452</v>
+        <v>6465</v>
       </c>
       <c r="M21" t="inlineStr"/>
     </row>
@@ -1325,22 +1325,22 @@
         <v>3.6</v>
       </c>
       <c r="G22" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>76436</v>
+        <v>76526</v>
       </c>
       <c r="I22" t="n">
-        <v>12.43</v>
+        <v>12.46</v>
       </c>
       <c r="J22" t="n">
-        <v>0.095</v>
+        <v>0.092</v>
       </c>
       <c r="K22" t="n">
-        <v>562</v>
+        <v>558</v>
       </c>
       <c r="L22" t="n">
-        <v>8323</v>
+        <v>8333</v>
       </c>
       <c r="M22" t="inlineStr"/>
     </row>
@@ -1369,19 +1369,19 @@
         <v>0.1</v>
       </c>
       <c r="H23" t="n">
-        <v>108340</v>
+        <v>108356</v>
       </c>
       <c r="I23" t="n">
-        <v>18.92</v>
+        <v>18.93</v>
       </c>
       <c r="J23" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="K23" t="n">
-        <v>1077</v>
+        <v>1073</v>
       </c>
       <c r="L23" t="n">
-        <v>5404</v>
+        <v>5427</v>
       </c>
       <c r="M23" t="inlineStr"/>
     </row>
@@ -1407,22 +1407,22 @@
         <v>3.5</v>
       </c>
       <c r="G24" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>75234</v>
+        <v>75299</v>
       </c>
       <c r="I24" t="n">
-        <v>12.29</v>
+        <v>12.31</v>
       </c>
       <c r="J24" t="n">
-        <v>0.095</v>
+        <v>0.092</v>
       </c>
       <c r="K24" t="n">
-        <v>614</v>
+        <v>610</v>
       </c>
       <c r="L24" t="n">
-        <v>7209</v>
+        <v>7228</v>
       </c>
       <c r="M24" t="inlineStr"/>
     </row>
@@ -1451,19 +1451,19 @@
         <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>50733</v>
+        <v>50809</v>
       </c>
       <c r="I25" t="n">
-        <v>6.94</v>
+        <v>6.96</v>
       </c>
       <c r="J25" t="n">
-        <v>0.101</v>
+        <v>0.099</v>
       </c>
       <c r="K25" t="n">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="L25" t="n">
-        <v>8657</v>
+        <v>8679</v>
       </c>
       <c r="M25" t="inlineStr"/>
     </row>
@@ -1489,22 +1489,22 @@
         <v>3.5</v>
       </c>
       <c r="G26" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H26" t="n">
-        <v>75688</v>
+        <v>75720</v>
       </c>
       <c r="I26" t="n">
-        <v>12.01</v>
+        <v>12.04</v>
       </c>
       <c r="J26" t="n">
-        <v>0.095</v>
+        <v>0.093</v>
       </c>
       <c r="K26" t="n">
-        <v>742</v>
+        <v>737</v>
       </c>
       <c r="L26" t="n">
-        <v>6426</v>
+        <v>6441</v>
       </c>
       <c r="M26" t="inlineStr"/>
     </row>
@@ -1533,19 +1533,19 @@
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>49507</v>
+        <v>49612</v>
       </c>
       <c r="I27" t="n">
-        <v>6.86</v>
+        <v>6.87</v>
       </c>
       <c r="J27" t="n">
-        <v>0.101</v>
+        <v>0.099</v>
       </c>
       <c r="K27" t="n">
         <v>353</v>
       </c>
       <c r="L27" t="n">
-        <v>7820</v>
+        <v>7839</v>
       </c>
       <c r="M27" t="inlineStr"/>
     </row>
@@ -1574,19 +1574,19 @@
         <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>33305</v>
+        <v>33397</v>
       </c>
       <c r="I28" t="n">
-        <v>3.24</v>
+        <v>3.26</v>
       </c>
       <c r="J28" t="n">
-        <v>0.106</v>
+        <v>0.104</v>
       </c>
       <c r="K28" t="n">
         <v>152</v>
       </c>
       <c r="L28" t="n">
-        <v>8794</v>
+        <v>8814</v>
       </c>
       <c r="M28" t="inlineStr"/>
     </row>
@@ -1615,19 +1615,19 @@
         <v>0</v>
       </c>
       <c r="H29" t="n">
-        <v>50187</v>
+        <v>50227</v>
       </c>
       <c r="I29" t="n">
-        <v>6.67</v>
+        <v>6.68</v>
       </c>
       <c r="J29" t="n">
-        <v>0.103</v>
+        <v>0.1</v>
       </c>
       <c r="K29" t="n">
-        <v>467</v>
+        <v>465</v>
       </c>
       <c r="L29" t="n">
-        <v>7236</v>
+        <v>7243</v>
       </c>
       <c r="M29" t="inlineStr"/>
     </row>
@@ -1656,19 +1656,19 @@
         <v>0</v>
       </c>
       <c r="H30" t="n">
-        <v>32246</v>
+        <v>32325</v>
       </c>
       <c r="I30" t="n">
-        <v>3.2</v>
+        <v>3.22</v>
       </c>
       <c r="J30" t="n">
-        <v>0.106</v>
+        <v>0.104</v>
       </c>
       <c r="K30" t="n">
         <v>177</v>
       </c>
       <c r="L30" t="n">
-        <v>8170</v>
+        <v>8179</v>
       </c>
       <c r="M30" t="inlineStr"/>
     </row>
@@ -1697,19 +1697,19 @@
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>23595</v>
+        <v>23772</v>
       </c>
       <c r="I31" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="J31" t="n">
-        <v>0.108</v>
+        <v>0.106</v>
       </c>
       <c r="K31" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="L31" t="n">
-        <v>8708</v>
+        <v>8714</v>
       </c>
       <c r="M31" t="inlineStr"/>
     </row>
@@ -1738,19 +1738,19 @@
         <v>0.1</v>
       </c>
       <c r="H32" t="n">
-        <v>117841</v>
+        <v>117786</v>
       </c>
       <c r="I32" t="n">
-        <v>19.71</v>
+        <v>19.74</v>
       </c>
       <c r="J32" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="K32" t="n">
-        <v>1424</v>
+        <v>1413</v>
       </c>
       <c r="L32" t="n">
-        <v>2367</v>
+        <v>2368</v>
       </c>
       <c r="M32" t="inlineStr"/>
     </row>
@@ -1776,19 +1776,19 @@
         <v>3.7</v>
       </c>
       <c r="G33" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>79034</v>
+        <v>79149</v>
       </c>
       <c r="I33" t="n">
-        <v>12.81</v>
+        <v>12.85</v>
       </c>
       <c r="J33" t="n">
-        <v>0.093</v>
+        <v>0.092</v>
       </c>
       <c r="K33" t="n">
-        <v>773</v>
+        <v>769</v>
       </c>
       <c r="L33" t="n">
         <v>4340</v>
@@ -1820,19 +1820,19 @@
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>51054</v>
+        <v>51225</v>
       </c>
       <c r="I34" t="n">
-        <v>7.19</v>
+        <v>7.23</v>
       </c>
       <c r="J34" t="n">
-        <v>0.101</v>
+        <v>0.099</v>
       </c>
       <c r="K34" t="n">
         <v>378</v>
       </c>
       <c r="L34" t="n">
-        <v>5910</v>
+        <v>5913</v>
       </c>
       <c r="M34" t="inlineStr"/>
     </row>
@@ -1858,22 +1858,22 @@
         <v>3.7</v>
       </c>
       <c r="G35" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>78819</v>
+        <v>78927</v>
       </c>
       <c r="I35" t="n">
-        <v>12.49</v>
+        <v>12.53</v>
       </c>
       <c r="J35" t="n">
-        <v>0.093</v>
+        <v>0.092</v>
       </c>
       <c r="K35" t="n">
-        <v>897</v>
+        <v>893</v>
       </c>
       <c r="L35" t="n">
-        <v>2464</v>
+        <v>2462</v>
       </c>
       <c r="M35" t="inlineStr"/>
     </row>
@@ -1902,19 +1902,19 @@
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>49455</v>
+        <v>49648</v>
       </c>
       <c r="I36" t="n">
-        <v>7.1</v>
+        <v>7.14</v>
       </c>
       <c r="J36" t="n">
-        <v>0.101</v>
+        <v>0.1</v>
       </c>
       <c r="K36" t="n">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="L36" t="n">
-        <v>3964</v>
+        <v>3966</v>
       </c>
       <c r="M36" t="inlineStr"/>
     </row>
@@ -1943,19 +1943,19 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>31776</v>
+        <v>31907</v>
       </c>
       <c r="I37" t="n">
-        <v>3.36</v>
+        <v>3.39</v>
       </c>
       <c r="J37" t="n">
-        <v>0.106</v>
+        <v>0.104</v>
       </c>
       <c r="K37" t="n">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="L37" t="n">
-        <v>4989</v>
+        <v>4997</v>
       </c>
       <c r="M37" t="inlineStr"/>
     </row>
@@ -1984,19 +1984,19 @@
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>49814</v>
+        <v>49925</v>
       </c>
       <c r="I38" t="n">
-        <v>6.9</v>
+        <v>6.93</v>
       </c>
       <c r="J38" t="n">
-        <v>0.101</v>
+        <v>0.1</v>
       </c>
       <c r="K38" t="n">
-        <v>528</v>
+        <v>526</v>
       </c>
       <c r="L38" t="n">
-        <v>2747</v>
+        <v>2749</v>
       </c>
       <c r="M38" t="inlineStr"/>
     </row>
@@ -2025,19 +2025,19 @@
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>30408</v>
+        <v>30539</v>
       </c>
       <c r="I39" t="n">
-        <v>3.31</v>
+        <v>3.34</v>
       </c>
       <c r="J39" t="n">
-        <v>0.106</v>
+        <v>0.104</v>
       </c>
       <c r="K39" t="n">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="L39" t="n">
-        <v>3729</v>
+        <v>3736</v>
       </c>
       <c r="M39" t="inlineStr"/>
     </row>
@@ -2066,19 +2066,19 @@
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>21191</v>
+        <v>21371</v>
       </c>
       <c r="I40" t="n">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="J40" t="n">
-        <v>0.108</v>
+        <v>0.106</v>
       </c>
       <c r="K40" t="n">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="L40" t="n">
-        <v>4295</v>
+        <v>4300</v>
       </c>
       <c r="M40" t="inlineStr"/>
     </row>
@@ -2107,19 +2107,19 @@
         <v>0</v>
       </c>
       <c r="H41" t="n">
-        <v>31002</v>
+        <v>31052</v>
       </c>
       <c r="I41" t="n">
-        <v>3.21</v>
+        <v>3.24</v>
       </c>
       <c r="J41" t="n">
-        <v>0.107</v>
+        <v>0.104</v>
       </c>
       <c r="K41" t="n">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="L41" t="n">
-        <v>3064</v>
+        <v>3061</v>
       </c>
       <c r="M41" t="inlineStr"/>
     </row>
@@ -2148,19 +2148,19 @@
         <v>0</v>
       </c>
       <c r="H42" t="n">
-        <v>20076</v>
+        <v>20253</v>
       </c>
       <c r="I42" t="n">
-        <v>1.21</v>
+        <v>1.24</v>
       </c>
       <c r="J42" t="n">
-        <v>0.108</v>
+        <v>0.106</v>
       </c>
       <c r="K42" t="n">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="L42" t="n">
-        <v>3607</v>
+        <v>3602</v>
       </c>
       <c r="M42" t="inlineStr"/>
     </row>
@@ -2189,19 +2189,19 @@
         <v>0</v>
       </c>
       <c r="H43" t="n">
-        <v>16842</v>
+        <v>16942</v>
       </c>
       <c r="I43" t="n">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="J43" t="n">
-        <v>0.109</v>
+        <v>0.107</v>
       </c>
       <c r="K43" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="L43" t="n">
-        <v>3845</v>
+        <v>3844</v>
       </c>
       <c r="M43" t="inlineStr"/>
     </row>
@@ -2230,19 +2230,19 @@
         <v>0</v>
       </c>
       <c r="H44" t="n">
-        <v>20720</v>
+        <v>20827</v>
       </c>
       <c r="I44" t="n">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="J44" t="n">
-        <v>0.108</v>
+        <v>0.106</v>
       </c>
       <c r="K44" t="n">
         <v>145</v>
       </c>
       <c r="L44" t="n">
-        <v>3271</v>
+        <v>3260</v>
       </c>
       <c r="M44" t="inlineStr"/>
     </row>
@@ -2271,19 +2271,19 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>15946</v>
+        <v>16059</v>
       </c>
       <c r="I45" t="n">
-        <v>0.33</v>
+        <v>0.35</v>
       </c>
       <c r="J45" t="n">
-        <v>0.109</v>
+        <v>0.107</v>
       </c>
       <c r="K45" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="L45" t="n">
-        <v>3500</v>
+        <v>3493</v>
       </c>
       <c r="M45" t="inlineStr"/>
     </row>
@@ -2312,19 +2312,19 @@
         <v>0</v>
       </c>
       <c r="H46" t="n">
-        <v>15831</v>
+        <v>15868</v>
       </c>
       <c r="I46" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J46" t="n">
-        <v>0.109</v>
+        <v>0.108</v>
       </c>
       <c r="K46" t="n">
         <v>4</v>
       </c>
       <c r="L46" t="n">
-        <v>3571</v>
+        <v>3567</v>
       </c>
       <c r="M46" t="inlineStr"/>
     </row>
@@ -2353,19 +2353,19 @@
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>77354</v>
+        <v>77429</v>
       </c>
       <c r="I47" t="n">
-        <v>10.56</v>
+        <v>10.63</v>
       </c>
       <c r="J47" t="n">
-        <v>0.098</v>
+        <v>0.096</v>
       </c>
       <c r="K47" t="n">
-        <v>1128</v>
+        <v>1118</v>
       </c>
       <c r="L47" t="n">
-        <v>1775</v>
+        <v>1772</v>
       </c>
       <c r="M47" t="inlineStr"/>
     </row>
@@ -2394,19 +2394,19 @@
         <v>0</v>
       </c>
       <c r="H48" t="n">
-        <v>42408</v>
+        <v>42482</v>
       </c>
       <c r="I48" t="n">
-        <v>5.05</v>
+        <v>5.07</v>
       </c>
       <c r="J48" t="n">
-        <v>0.103</v>
+        <v>0.102</v>
       </c>
       <c r="K48" t="n">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="L48" t="n">
-        <v>3397</v>
+        <v>3409</v>
       </c>
       <c r="M48" t="inlineStr"/>
     </row>
@@ -2435,19 +2435,19 @@
         <v>0</v>
       </c>
       <c r="H49" t="n">
-        <v>23841</v>
+        <v>23962</v>
       </c>
       <c r="I49" t="n">
-        <v>1.67</v>
+        <v>1.7</v>
       </c>
       <c r="J49" t="n">
-        <v>0.107</v>
+        <v>0.106</v>
       </c>
       <c r="K49" t="n">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="L49" t="n">
-        <v>4371</v>
+        <v>4382</v>
       </c>
       <c r="M49" t="inlineStr"/>
     </row>
@@ -2476,19 +2476,19 @@
         <v>0</v>
       </c>
       <c r="H50" t="n">
-        <v>42287</v>
+        <v>42291</v>
       </c>
       <c r="I50" t="n">
-        <v>4.81</v>
+        <v>4.82</v>
       </c>
       <c r="J50" t="n">
-        <v>0.103</v>
+        <v>0.102</v>
       </c>
       <c r="K50" t="n">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="L50" t="n">
-        <v>1189</v>
+        <v>1192</v>
       </c>
       <c r="M50" t="inlineStr"/>
     </row>
@@ -2517,19 +2517,19 @@
         <v>0</v>
       </c>
       <c r="H51" t="n">
-        <v>21984</v>
+        <v>22093</v>
       </c>
       <c r="I51" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="J51" t="n">
-        <v>0.107</v>
+        <v>0.106</v>
       </c>
       <c r="K51" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="L51" t="n">
-        <v>2101</v>
+        <v>2100</v>
       </c>
       <c r="M51" t="inlineStr"/>
     </row>
@@ -2558,19 +2558,19 @@
         <v>0</v>
       </c>
       <c r="H52" t="n">
-        <v>16132</v>
+        <v>16268</v>
       </c>
       <c r="I52" t="n">
-        <v>0.39</v>
+        <v>0.41</v>
       </c>
       <c r="J52" t="n">
-        <v>0.109</v>
+        <v>0.107</v>
       </c>
       <c r="K52" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="L52" t="n">
-        <v>2449</v>
+        <v>2451</v>
       </c>
       <c r="M52" t="inlineStr"/>
     </row>
@@ -2599,19 +2599,19 @@
         <v>0</v>
       </c>
       <c r="H53" t="n">
-        <v>22145</v>
+        <v>22160</v>
       </c>
       <c r="I53" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="J53" t="n">
-        <v>0.107</v>
+        <v>0.106</v>
       </c>
       <c r="K53" t="n">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="L53" t="n">
-        <v>789</v>
+        <v>777</v>
       </c>
       <c r="M53" t="inlineStr"/>
     </row>
@@ -2640,19 +2640,19 @@
         <v>0</v>
       </c>
       <c r="H54" t="n">
-        <v>14696</v>
+        <v>14837</v>
       </c>
       <c r="I54" t="n">
-        <v>0.39</v>
+        <v>0.41</v>
       </c>
       <c r="J54" t="n">
-        <v>0.109</v>
+        <v>0.107</v>
       </c>
       <c r="K54" t="n">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="L54" t="n">
-        <v>1116</v>
+        <v>1107</v>
       </c>
       <c r="M54" t="inlineStr"/>
     </row>
@@ -2681,19 +2681,19 @@
         <v>0</v>
       </c>
       <c r="H55" t="n">
-        <v>14239</v>
+        <v>14284</v>
       </c>
       <c r="I55" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="J55" t="n">
-        <v>0.109</v>
+        <v>0.108</v>
       </c>
       <c r="K55" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L55" t="n">
-        <v>1203</v>
+        <v>1197</v>
       </c>
       <c r="M55" t="inlineStr"/>
     </row>
@@ -2722,19 +2722,19 @@
         <v>0</v>
       </c>
       <c r="H56" t="n">
-        <v>15284</v>
+        <v>15337</v>
       </c>
       <c r="I56" t="n">
-        <v>0.37</v>
+        <v>0.39</v>
       </c>
       <c r="J56" t="n">
-        <v>0.109</v>
+        <v>0.107</v>
       </c>
       <c r="K56" t="n">
         <v>89</v>
       </c>
       <c r="L56" t="n">
-        <v>673</v>
+        <v>669</v>
       </c>
       <c r="M56" t="inlineStr"/>
     </row>
@@ -2763,25 +2763,21 @@
         <v>0</v>
       </c>
       <c r="H57" t="n">
-        <v>13381</v>
+        <v>13431</v>
       </c>
       <c r="I57" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="J57" t="n">
-        <v>0.109</v>
+        <v>0.108</v>
       </c>
       <c r="K57" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L57" t="n">
-        <v>755</v>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>SI</t>
-        </is>
-      </c>
+        <v>754</v>
+      </c>
+      <c r="M57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2808,19 +2804,19 @@
         <v>0</v>
       </c>
       <c r="H58" t="n">
-        <v>14258</v>
+        <v>14285</v>
       </c>
       <c r="I58" t="n">
         <v>0.01</v>
       </c>
       <c r="J58" t="n">
-        <v>0.11</v>
+        <v>0.108</v>
       </c>
       <c r="K58" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L58" t="n">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="M58" t="inlineStr"/>
     </row>
@@ -2849,19 +2845,19 @@
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>14109</v>
+        <v>14107</v>
       </c>
       <c r="I59" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="J59" t="n">
-        <v>0.109</v>
+        <v>0.108</v>
       </c>
       <c r="K59" t="n">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L59" t="n">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="M59" t="inlineStr"/>
     </row>
@@ -2890,19 +2886,19 @@
         <v>0</v>
       </c>
       <c r="H60" t="n">
-        <v>13681</v>
+        <v>13703</v>
       </c>
       <c r="I60" t="n">
         <v>0.01</v>
       </c>
       <c r="J60" t="n">
-        <v>0.11</v>
+        <v>0.108</v>
       </c>
       <c r="K60" t="n">
         <v>1</v>
       </c>
       <c r="L60" t="n">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="M60" t="inlineStr"/>
     </row>
@@ -2931,13 +2927,13 @@
         <v>0</v>
       </c>
       <c r="H61" t="n">
-        <v>14857</v>
+        <v>14865</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>0.11</v>
+        <v>0.108</v>
       </c>
       <c r="K61" t="n">
         <v>0</v>
@@ -2972,19 +2968,19 @@
         <v>0</v>
       </c>
       <c r="H62" t="n">
-        <v>68719</v>
+        <v>68916</v>
       </c>
       <c r="I62" t="n">
-        <v>8.44</v>
+        <v>8.51</v>
       </c>
       <c r="J62" t="n">
-        <v>0.1</v>
+        <v>0.098</v>
       </c>
       <c r="K62" t="n">
-        <v>1059</v>
+        <v>1055</v>
       </c>
       <c r="L62" t="n">
-        <v>1624</v>
+        <v>1629</v>
       </c>
       <c r="M62" t="inlineStr"/>
     </row>
@@ -3013,19 +3009,19 @@
         <v>0</v>
       </c>
       <c r="H63" t="n">
-        <v>34709</v>
+        <v>34844</v>
       </c>
       <c r="I63" t="n">
-        <v>3.29</v>
+        <v>3.32</v>
       </c>
       <c r="J63" t="n">
         <v>0.104</v>
       </c>
       <c r="K63" t="n">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="L63" t="n">
-        <v>3154</v>
+        <v>3174</v>
       </c>
       <c r="M63" t="inlineStr"/>
     </row>
@@ -3054,19 +3050,19 @@
         <v>0</v>
       </c>
       <c r="H64" t="n">
-        <v>19244</v>
+        <v>19255</v>
       </c>
       <c r="I64" t="n">
         <v>0.64</v>
       </c>
       <c r="J64" t="n">
-        <v>0.109</v>
+        <v>0.107</v>
       </c>
       <c r="K64" t="n">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="L64" t="n">
-        <v>3936</v>
+        <v>3965</v>
       </c>
       <c r="M64" t="inlineStr"/>
     </row>
@@ -3095,19 +3091,19 @@
         <v>0</v>
       </c>
       <c r="H65" t="n">
-        <v>34594</v>
+        <v>34680</v>
       </c>
       <c r="I65" t="n">
-        <v>3.09</v>
+        <v>3.11</v>
       </c>
       <c r="J65" t="n">
-        <v>0.105</v>
+        <v>0.104</v>
       </c>
       <c r="K65" t="n">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="L65" t="n">
-        <v>856</v>
+        <v>863</v>
       </c>
       <c r="M65" t="inlineStr"/>
     </row>
@@ -3136,19 +3132,19 @@
         <v>0</v>
       </c>
       <c r="H66" t="n">
-        <v>17329</v>
+        <v>17327</v>
       </c>
       <c r="I66" t="n">
         <v>0.62</v>
       </c>
       <c r="J66" t="n">
-        <v>0.109</v>
+        <v>0.107</v>
       </c>
       <c r="K66" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L66" t="n">
-        <v>1580</v>
+        <v>1593</v>
       </c>
       <c r="M66" t="inlineStr"/>
     </row>
@@ -3177,19 +3173,19 @@
         <v>0</v>
       </c>
       <c r="H67" t="n">
-        <v>14828</v>
+        <v>14834</v>
       </c>
       <c r="I67" t="n">
         <v>0.05</v>
       </c>
       <c r="J67" t="n">
-        <v>0.11</v>
+        <v>0.108</v>
       </c>
       <c r="K67" t="n">
         <v>5</v>
       </c>
       <c r="L67" t="n">
-        <v>1743</v>
+        <v>1757</v>
       </c>
       <c r="M67" t="inlineStr"/>
     </row>
@@ -3218,19 +3214,19 @@
         <v>0</v>
       </c>
       <c r="H68" t="n">
-        <v>17433</v>
+        <v>17346</v>
       </c>
       <c r="I68" t="n">
         <v>0.57</v>
       </c>
       <c r="J68" t="n">
-        <v>0.109</v>
+        <v>0.107</v>
       </c>
       <c r="K68" t="n">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="L68" t="n">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="M68" t="inlineStr"/>
     </row>
@@ -3259,21 +3255,25 @@
         <v>0</v>
       </c>
       <c r="H69" t="n">
-        <v>13414</v>
+        <v>13417</v>
       </c>
       <c r="I69" t="n">
         <v>0.05</v>
       </c>
       <c r="J69" t="n">
-        <v>0.11</v>
+        <v>0.108</v>
       </c>
       <c r="K69" t="n">
         <v>6</v>
       </c>
       <c r="L69" t="n">
-        <v>400</v>
-      </c>
-      <c r="M69" t="inlineStr"/>
+        <v>405</v>
+      </c>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>SI</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -3300,19 +3300,19 @@
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>14319</v>
+        <v>14334</v>
       </c>
       <c r="I70" t="n">
         <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>0.11</v>
+        <v>0.108</v>
       </c>
       <c r="K70" t="n">
         <v>0</v>
       </c>
       <c r="L70" t="n">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="M70" t="inlineStr"/>
     </row>
@@ -3341,19 +3341,19 @@
         <v>0</v>
       </c>
       <c r="H71" t="n">
-        <v>13987</v>
+        <v>13937</v>
       </c>
       <c r="I71" t="n">
         <v>0.04</v>
       </c>
       <c r="J71" t="n">
-        <v>0.11</v>
+        <v>0.108</v>
       </c>
       <c r="K71" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="L71" t="n">
-        <v>50</v>
+        <v>56</v>
       </c>
       <c r="M71" t="inlineStr"/>
     </row>
@@ -3382,19 +3382,19 @@
         <v>0</v>
       </c>
       <c r="H72" t="n">
-        <v>13578</v>
+        <v>13592</v>
       </c>
       <c r="I72" t="n">
         <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>0.11</v>
+        <v>0.108</v>
       </c>
       <c r="K72" t="n">
         <v>0</v>
       </c>
       <c r="L72" t="n">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="M72" t="inlineStr"/>
     </row>
@@ -3429,13 +3429,13 @@
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>0.11</v>
+        <v>0.108</v>
       </c>
       <c r="K73" t="n">
         <v>0</v>
       </c>
       <c r="L73" t="n">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="M73" t="inlineStr"/>
     </row>
@@ -3464,19 +3464,19 @@
         <v>0</v>
       </c>
       <c r="H74" t="n">
-        <v>14353</v>
+        <v>14304</v>
       </c>
       <c r="I74" t="n">
         <v>0</v>
       </c>
       <c r="J74" t="n">
-        <v>0.11</v>
+        <v>0.108</v>
       </c>
       <c r="K74" t="n">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="L74" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="M74" t="inlineStr"/>
     </row>
@@ -3511,13 +3511,13 @@
         <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>0.11</v>
+        <v>0.108</v>
       </c>
       <c r="K75" t="n">
         <v>0</v>
       </c>
       <c r="L75" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="M75" t="inlineStr"/>
     </row>
@@ -3546,19 +3546,19 @@
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>15504</v>
+        <v>15502</v>
       </c>
       <c r="I76" t="n">
         <v>0</v>
       </c>
       <c r="J76" t="n">
-        <v>0.11</v>
+        <v>0.108</v>
       </c>
       <c r="K76" t="n">
         <v>0</v>
       </c>
       <c r="L76" t="n">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="M76" t="inlineStr"/>
     </row>
@@ -3587,19 +3587,19 @@
         <v>0</v>
       </c>
       <c r="H77" t="n">
-        <v>69276</v>
+        <v>69385</v>
       </c>
       <c r="I77" t="n">
-        <v>8.33</v>
+        <v>8.390000000000001</v>
       </c>
       <c r="J77" t="n">
-        <v>0.101</v>
+        <v>0.099</v>
       </c>
       <c r="K77" t="n">
-        <v>1057</v>
+        <v>1052</v>
       </c>
       <c r="L77" t="n">
-        <v>1617</v>
+        <v>1621</v>
       </c>
       <c r="M77" t="inlineStr"/>
     </row>
@@ -3628,19 +3628,19 @@
         <v>0</v>
       </c>
       <c r="H78" t="n">
-        <v>35315</v>
+        <v>35374</v>
       </c>
       <c r="I78" t="n">
-        <v>3.2</v>
+        <v>3.23</v>
       </c>
       <c r="J78" t="n">
-        <v>0.105</v>
+        <v>0.104</v>
       </c>
       <c r="K78" t="n">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="L78" t="n">
-        <v>3142</v>
+        <v>3160</v>
       </c>
       <c r="M78" t="inlineStr"/>
     </row>
@@ -3669,19 +3669,19 @@
         <v>0</v>
       </c>
       <c r="H79" t="n">
-        <v>19973</v>
+        <v>19946</v>
       </c>
       <c r="I79" t="n">
         <v>0.59</v>
       </c>
       <c r="J79" t="n">
-        <v>0.109</v>
+        <v>0.107</v>
       </c>
       <c r="K79" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="L79" t="n">
-        <v>3914</v>
+        <v>3940</v>
       </c>
       <c r="M79" t="inlineStr"/>
     </row>
@@ -3710,19 +3710,19 @@
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>35185</v>
+        <v>35204</v>
       </c>
       <c r="I80" t="n">
-        <v>3</v>
+        <v>3.02</v>
       </c>
       <c r="J80" t="n">
-        <v>0.105</v>
+        <v>0.104</v>
       </c>
       <c r="K80" t="n">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="L80" t="n">
-        <v>838</v>
+        <v>843</v>
       </c>
       <c r="M80" t="inlineStr"/>
     </row>
@@ -3751,19 +3751,19 @@
         <v>0</v>
       </c>
       <c r="H81" t="n">
-        <v>18048</v>
+        <v>18008</v>
       </c>
       <c r="I81" t="n">
         <v>0.57</v>
       </c>
       <c r="J81" t="n">
-        <v>0.109</v>
+        <v>0.107</v>
       </c>
       <c r="K81" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="L81" t="n">
-        <v>1553</v>
+        <v>1562</v>
       </c>
       <c r="M81" t="inlineStr"/>
     </row>
@@ -3792,19 +3792,19 @@
         <v>0</v>
       </c>
       <c r="H82" t="n">
-        <v>15740</v>
+        <v>15722</v>
       </c>
       <c r="I82" t="n">
         <v>0.04</v>
       </c>
       <c r="J82" t="n">
-        <v>0.11</v>
+        <v>0.108</v>
       </c>
       <c r="K82" t="n">
         <v>4</v>
       </c>
       <c r="L82" t="n">
-        <v>1706</v>
+        <v>1715</v>
       </c>
       <c r="M82" t="inlineStr"/>
     </row>
@@ -3833,19 +3833,19 @@
         <v>0</v>
       </c>
       <c r="H83" t="n">
-        <v>18156</v>
+        <v>18026</v>
       </c>
       <c r="I83" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="J83" t="n">
-        <v>0.109</v>
+        <v>0.107</v>
       </c>
       <c r="K83" t="n">
-        <v>140</v>
+        <v>135</v>
       </c>
       <c r="L83" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="M83" t="inlineStr"/>
     </row>
@@ -3874,13 +3874,13 @@
         <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>14328</v>
+        <v>14307</v>
       </c>
       <c r="I84" t="n">
         <v>0.04</v>
       </c>
       <c r="J84" t="n">
-        <v>0.11</v>
+        <v>0.108</v>
       </c>
       <c r="K84" t="n">
         <v>5</v>
@@ -3915,19 +3915,19 @@
         <v>0</v>
       </c>
       <c r="H85" t="n">
-        <v>15275</v>
+        <v>15274</v>
       </c>
       <c r="I85" t="n">
         <v>0</v>
       </c>
       <c r="J85" t="n">
-        <v>0.11</v>
+        <v>0.108</v>
       </c>
       <c r="K85" t="n">
         <v>0</v>
       </c>
       <c r="L85" t="n">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="M85" t="inlineStr"/>
     </row>
@@ -3956,19 +3956,19 @@
         <v>0</v>
       </c>
       <c r="H86" t="n">
-        <v>14902</v>
+        <v>14826</v>
       </c>
       <c r="I86" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="J86" t="n">
-        <v>0.11</v>
+        <v>0.108</v>
       </c>
       <c r="K86" t="n">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="L86" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M86" t="inlineStr"/>
     </row>
@@ -3997,13 +3997,13 @@
         <v>0</v>
       </c>
       <c r="H87" t="n">
-        <v>14543</v>
+        <v>14542</v>
       </c>
       <c r="I87" t="n">
         <v>0</v>
       </c>
       <c r="J87" t="n">
-        <v>0.11</v>
+        <v>0.108</v>
       </c>
       <c r="K87" t="n">
         <v>0</v>
@@ -4038,13 +4038,13 @@
         <v>0</v>
       </c>
       <c r="H88" t="n">
-        <v>15764</v>
+        <v>15759</v>
       </c>
       <c r="I88" t="n">
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>0.11</v>
+        <v>0.108</v>
       </c>
       <c r="K88" t="n">
         <v>0</v>
@@ -4079,16 +4079,16 @@
         <v>0</v>
       </c>
       <c r="H89" t="n">
-        <v>15320</v>
+        <v>15256</v>
       </c>
       <c r="I89" t="n">
         <v>0</v>
       </c>
       <c r="J89" t="n">
-        <v>0.11</v>
+        <v>0.108</v>
       </c>
       <c r="K89" t="n">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="L89" t="n">
         <v>1</v>
@@ -4120,13 +4120,13 @@
         <v>0</v>
       </c>
       <c r="H90" t="n">
-        <v>15251</v>
+        <v>15246</v>
       </c>
       <c r="I90" t="n">
         <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>0.11</v>
+        <v>0.108</v>
       </c>
       <c r="K90" t="n">
         <v>0</v>
@@ -4161,13 +4161,13 @@
         <v>0</v>
       </c>
       <c r="H91" t="n">
-        <v>16474</v>
+        <v>16469</v>
       </c>
       <c r="I91" t="n">
         <v>0</v>
       </c>
       <c r="J91" t="n">
-        <v>0.11</v>
+        <v>0.108</v>
       </c>
       <c r="K91" t="n">
         <v>0</v>
@@ -4196,25 +4196,25 @@
         <v>20</v>
       </c>
       <c r="F92" t="n">
-        <v>22.1</v>
+        <v>21.9</v>
       </c>
       <c r="G92" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="H92" t="n">
-        <v>216697</v>
+        <v>216267</v>
       </c>
       <c r="I92" t="n">
-        <v>51.24</v>
+        <v>51.11</v>
       </c>
       <c r="J92" t="n">
         <v>0.052</v>
       </c>
       <c r="K92" t="n">
-        <v>2131</v>
+        <v>2127</v>
       </c>
       <c r="L92" t="n">
-        <v>3068</v>
+        <v>3071</v>
       </c>
       <c r="M92" t="inlineStr"/>
     </row>
@@ -4237,25 +4237,25 @@
         <v>25</v>
       </c>
       <c r="F93" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="G93" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="H93" t="n">
-        <v>171220</v>
+        <v>170828</v>
       </c>
       <c r="I93" t="n">
-        <v>40.14</v>
+        <v>40.02</v>
       </c>
       <c r="J93" t="n">
-        <v>0.059</v>
+        <v>0.06</v>
       </c>
       <c r="K93" t="n">
-        <v>1538</v>
+        <v>1535</v>
       </c>
       <c r="L93" t="n">
-        <v>5041</v>
+        <v>5043</v>
       </c>
       <c r="M93" t="inlineStr"/>
     </row>
@@ -4278,25 +4278,25 @@
         <v>30</v>
       </c>
       <c r="F94" t="n">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="G94" t="n">
         <v>0.1</v>
       </c>
       <c r="H94" t="n">
-        <v>130324</v>
+        <v>129913</v>
       </c>
       <c r="I94" t="n">
-        <v>29.58</v>
+        <v>29.47</v>
       </c>
       <c r="J94" t="n">
-        <v>0.073</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="K94" t="n">
-        <v>1062</v>
+        <v>1057</v>
       </c>
       <c r="L94" t="n">
-        <v>6980</v>
+        <v>6986</v>
       </c>
       <c r="M94" t="inlineStr"/>
     </row>
@@ -4319,25 +4319,25 @@
         <v>25</v>
       </c>
       <c r="F95" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="G95" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="H95" t="n">
-        <v>172038</v>
+        <v>171576</v>
       </c>
       <c r="I95" t="n">
-        <v>39.92</v>
+        <v>39.82</v>
       </c>
       <c r="J95" t="n">
-        <v>0.063</v>
+        <v>0.06</v>
       </c>
       <c r="K95" t="n">
-        <v>1666</v>
+        <v>1658</v>
       </c>
       <c r="L95" t="n">
-        <v>4355</v>
+        <v>4356</v>
       </c>
       <c r="M95" t="inlineStr"/>
     </row>
@@ -4366,19 +4366,19 @@
         <v>0.1</v>
       </c>
       <c r="H96" t="n">
-        <v>129617</v>
+        <v>129190</v>
       </c>
       <c r="I96" t="n">
-        <v>29.56</v>
+        <v>29.45</v>
       </c>
       <c r="J96" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="K96" t="n">
-        <v>1116</v>
+        <v>1110</v>
       </c>
       <c r="L96" t="n">
-        <v>6023</v>
+        <v>6029</v>
       </c>
       <c r="M96" t="inlineStr"/>
     </row>
@@ -4407,19 +4407,19 @@
         <v>0.1</v>
       </c>
       <c r="H97" t="n">
-        <v>93638</v>
+        <v>93318</v>
       </c>
       <c r="I97" t="n">
-        <v>20.14</v>
+        <v>20.07</v>
       </c>
       <c r="J97" t="n">
-        <v>0.083</v>
+        <v>0.08</v>
       </c>
       <c r="K97" t="n">
-        <v>708</v>
+        <v>703</v>
       </c>
       <c r="L97" t="n">
-        <v>7680</v>
+        <v>7676</v>
       </c>
       <c r="M97" t="inlineStr"/>
     </row>
@@ -4448,19 +4448,19 @@
         <v>0.1</v>
       </c>
       <c r="H98" t="n">
-        <v>132119</v>
+        <v>131759</v>
       </c>
       <c r="I98" t="n">
-        <v>29.57</v>
+        <v>29.46</v>
       </c>
       <c r="J98" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="K98" t="n">
-        <v>1274</v>
+        <v>1271</v>
       </c>
       <c r="L98" t="n">
-        <v>5656</v>
+        <v>5660</v>
       </c>
       <c r="M98" t="inlineStr"/>
     </row>
@@ -4489,19 +4489,19 @@
         <v>0.1</v>
       </c>
       <c r="H99" t="n">
-        <v>93440</v>
+        <v>93063</v>
       </c>
       <c r="I99" t="n">
-        <v>20.2</v>
+        <v>20.12</v>
       </c>
       <c r="J99" t="n">
-        <v>0.083</v>
+        <v>0.08</v>
       </c>
       <c r="K99" t="n">
-        <v>764</v>
+        <v>758</v>
       </c>
       <c r="L99" t="n">
-        <v>6964</v>
+        <v>6963</v>
       </c>
       <c r="M99" t="inlineStr"/>
     </row>
@@ -4530,19 +4530,19 @@
         <v>0.1</v>
       </c>
       <c r="H100" t="n">
-        <v>63437</v>
+        <v>63241</v>
       </c>
       <c r="I100" t="n">
-        <v>12.25</v>
+        <v>12.21</v>
       </c>
       <c r="J100" t="n">
-        <v>0.094</v>
+        <v>0.091</v>
       </c>
       <c r="K100" t="n">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="L100" t="n">
-        <v>8279</v>
+        <v>8268</v>
       </c>
       <c r="M100" t="inlineStr"/>
     </row>
@@ -4571,19 +4571,19 @@
         <v>0.1</v>
       </c>
       <c r="H101" t="n">
-        <v>98878</v>
+        <v>98535</v>
       </c>
       <c r="I101" t="n">
-        <v>20.68</v>
+        <v>20.62</v>
       </c>
       <c r="J101" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.082</v>
       </c>
       <c r="K101" t="n">
-        <v>973</v>
+        <v>965</v>
       </c>
       <c r="L101" t="n">
-        <v>6806</v>
+        <v>6796</v>
       </c>
       <c r="M101" t="inlineStr"/>
     </row>
@@ -4612,19 +4612,19 @@
         <v>0.1</v>
       </c>
       <c r="H102" t="n">
-        <v>63783</v>
+        <v>63547</v>
       </c>
       <c r="I102" t="n">
-        <v>12.44</v>
+        <v>12.41</v>
       </c>
       <c r="J102" t="n">
-        <v>0.092</v>
+        <v>0.09</v>
       </c>
       <c r="K102" t="n">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="L102" t="n">
-        <v>7721</v>
+        <v>7704</v>
       </c>
       <c r="M102" t="inlineStr"/>
     </row>
@@ -4650,22 +4650,22 @@
         <v>2.2</v>
       </c>
       <c r="G103" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H103" t="n">
-        <v>41253</v>
+        <v>41149</v>
       </c>
       <c r="I103" t="n">
         <v>6.41</v>
       </c>
       <c r="J103" t="n">
-        <v>0.1</v>
+        <v>0.098</v>
       </c>
       <c r="K103" t="n">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="L103" t="n">
-        <v>8640</v>
+        <v>8617</v>
       </c>
       <c r="M103" t="inlineStr"/>
     </row>
@@ -4694,7 +4694,7 @@
         <v>0.1</v>
       </c>
       <c r="H104" t="n">
-        <v>73461</v>
+        <v>73395</v>
       </c>
       <c r="I104" t="n">
         <v>13.82</v>
@@ -4703,10 +4703,10 @@
         <v>0.089</v>
       </c>
       <c r="K104" t="n">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="L104" t="n">
-        <v>7699</v>
+        <v>7673</v>
       </c>
       <c r="M104" t="inlineStr"/>
     </row>
@@ -4729,25 +4729,25 @@
         <v>45</v>
       </c>
       <c r="F105" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="G105" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H105" t="n">
-        <v>42332</v>
+        <v>42251</v>
       </c>
       <c r="I105" t="n">
-        <v>6.77</v>
+        <v>6.78</v>
       </c>
       <c r="J105" t="n">
-        <v>0.098</v>
+        <v>0.097</v>
       </c>
       <c r="K105" t="n">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="L105" t="n">
-        <v>8227</v>
+        <v>8203</v>
       </c>
       <c r="M105" t="inlineStr"/>
     </row>
@@ -4776,19 +4776,19 @@
         <v>0</v>
       </c>
       <c r="H106" t="n">
-        <v>27431</v>
+        <v>27425</v>
       </c>
       <c r="I106" t="n">
-        <v>2.82</v>
+        <v>2.81</v>
       </c>
       <c r="J106" t="n">
-        <v>0.103</v>
+        <v>0.101</v>
       </c>
       <c r="K106" t="n">
         <v>100</v>
       </c>
       <c r="L106" t="n">
-        <v>8747</v>
+        <v>8728</v>
       </c>
       <c r="M106" t="inlineStr"/>
     </row>
@@ -4811,22 +4811,22 @@
         <v>30</v>
       </c>
       <c r="F107" t="n">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="G107" t="n">
         <v>0.1</v>
       </c>
       <c r="H107" t="n">
-        <v>137730</v>
+        <v>137320</v>
       </c>
       <c r="I107" t="n">
-        <v>30.17</v>
+        <v>30.07</v>
       </c>
       <c r="J107" t="n">
-        <v>0.075</v>
+        <v>0.073</v>
       </c>
       <c r="K107" t="n">
-        <v>1522</v>
+        <v>1517</v>
       </c>
       <c r="L107" t="n">
         <v>1733</v>
@@ -4858,19 +4858,19 @@
         <v>0.1</v>
       </c>
       <c r="H108" t="n">
-        <v>96122</v>
+        <v>95744</v>
       </c>
       <c r="I108" t="n">
-        <v>20.67</v>
+        <v>20.58</v>
       </c>
       <c r="J108" t="n">
-        <v>0.082</v>
+        <v>0.081</v>
       </c>
       <c r="K108" t="n">
-        <v>914</v>
+        <v>908</v>
       </c>
       <c r="L108" t="n">
-        <v>3147</v>
+        <v>3144</v>
       </c>
       <c r="M108" t="inlineStr"/>
     </row>
@@ -4899,19 +4899,19 @@
         <v>0.1</v>
       </c>
       <c r="H109" t="n">
-        <v>63401</v>
+        <v>63299</v>
       </c>
       <c r="I109" t="n">
-        <v>12.5</v>
+        <v>12.48</v>
       </c>
       <c r="J109" t="n">
-        <v>0.091</v>
+        <v>0.089</v>
       </c>
       <c r="K109" t="n">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="L109" t="n">
-        <v>4493</v>
+        <v>4475</v>
       </c>
       <c r="M109" t="inlineStr"/>
     </row>
@@ -4940,19 +4940,19 @@
         <v>0.1</v>
       </c>
       <c r="H110" t="n">
-        <v>99251</v>
+        <v>99002</v>
       </c>
       <c r="I110" t="n">
-        <v>20.95</v>
+        <v>20.92</v>
       </c>
       <c r="J110" t="n">
-        <v>0.083</v>
+        <v>0.081</v>
       </c>
       <c r="K110" t="n">
-        <v>1068</v>
+        <v>1061</v>
       </c>
       <c r="L110" t="n">
-        <v>2113</v>
+        <v>2100</v>
       </c>
       <c r="M110" t="inlineStr"/>
     </row>
@@ -4981,19 +4981,19 @@
         <v>0.1</v>
       </c>
       <c r="H111" t="n">
-        <v>63091</v>
+        <v>62958</v>
       </c>
       <c r="I111" t="n">
-        <v>12.67</v>
+        <v>12.65</v>
       </c>
       <c r="J111" t="n">
-        <v>0.089</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="K111" t="n">
-        <v>543</v>
+        <v>540</v>
       </c>
       <c r="L111" t="n">
-        <v>3081</v>
+        <v>3060</v>
       </c>
       <c r="M111" t="inlineStr"/>
     </row>
@@ -5019,22 +5019,22 @@
         <v>2.1</v>
       </c>
       <c r="G112" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H112" t="n">
-        <v>39480</v>
+        <v>39414</v>
       </c>
       <c r="I112" t="n">
-        <v>6.56</v>
+        <v>6.57</v>
       </c>
       <c r="J112" t="n">
         <v>0.098</v>
       </c>
       <c r="K112" t="n">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="L112" t="n">
-        <v>4014</v>
+        <v>3993</v>
       </c>
       <c r="M112" t="inlineStr"/>
     </row>
@@ -5063,19 +5063,19 @@
         <v>0.1</v>
       </c>
       <c r="H113" t="n">
-        <v>71768</v>
+        <v>71721</v>
       </c>
       <c r="I113" t="n">
-        <v>13.96</v>
+        <v>13.97</v>
       </c>
       <c r="J113" t="n">
         <v>0.08799999999999999</v>
       </c>
       <c r="K113" t="n">
-        <v>779</v>
+        <v>775</v>
       </c>
       <c r="L113" t="n">
-        <v>2692</v>
+        <v>2670</v>
       </c>
       <c r="M113" t="inlineStr"/>
     </row>
@@ -5101,22 +5101,22 @@
         <v>2.1</v>
       </c>
       <c r="G114" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H114" t="n">
-        <v>40233</v>
+        <v>40190</v>
       </c>
       <c r="I114" t="n">
-        <v>6.9</v>
+        <v>6.91</v>
       </c>
       <c r="J114" t="n">
-        <v>0.098</v>
+        <v>0.097</v>
       </c>
       <c r="K114" t="n">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="L114" t="n">
-        <v>3240</v>
+        <v>3220</v>
       </c>
       <c r="M114" t="inlineStr"/>
     </row>
@@ -5145,19 +5145,19 @@
         <v>0</v>
       </c>
       <c r="H115" t="n">
-        <v>24806</v>
+        <v>24798</v>
       </c>
       <c r="I115" t="n">
         <v>2.86</v>
       </c>
       <c r="J115" t="n">
-        <v>0.103</v>
+        <v>0.101</v>
       </c>
       <c r="K115" t="n">
         <v>108</v>
       </c>
       <c r="L115" t="n">
-        <v>3776</v>
+        <v>3762</v>
       </c>
       <c r="M115" t="inlineStr"/>
     </row>
@@ -5186,19 +5186,19 @@
         <v>0</v>
       </c>
       <c r="H116" t="n">
-        <v>55443</v>
+        <v>55380</v>
       </c>
       <c r="I116" t="n">
-        <v>9.58</v>
+        <v>9.57</v>
       </c>
       <c r="J116" t="n">
-        <v>0.094</v>
+        <v>0.093</v>
       </c>
       <c r="K116" t="n">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="L116" t="n">
-        <v>3147</v>
+        <v>3129</v>
       </c>
       <c r="M116" t="inlineStr"/>
     </row>
@@ -5227,19 +5227,19 @@
         <v>0</v>
       </c>
       <c r="H117" t="n">
-        <v>26974</v>
+        <v>26871</v>
       </c>
       <c r="I117" t="n">
-        <v>3.46</v>
+        <v>3.44</v>
       </c>
       <c r="J117" t="n">
-        <v>0.102</v>
+        <v>0.1</v>
       </c>
       <c r="K117" t="n">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="L117" t="n">
-        <v>3395</v>
+        <v>3379</v>
       </c>
       <c r="M117" t="inlineStr"/>
     </row>
@@ -5268,19 +5268,19 @@
         <v>0</v>
       </c>
       <c r="H118" t="n">
-        <v>17909</v>
+        <v>17844</v>
       </c>
       <c r="I118" t="n">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="J118" t="n">
-        <v>0.107</v>
+        <v>0.104</v>
       </c>
       <c r="K118" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="L118" t="n">
-        <v>3640</v>
+        <v>3624</v>
       </c>
       <c r="M118" t="inlineStr"/>
     </row>
@@ -5309,19 +5309,19 @@
         <v>0</v>
       </c>
       <c r="H119" t="n">
-        <v>47789</v>
+        <v>47756</v>
       </c>
       <c r="I119" t="n">
         <v>7.4</v>
       </c>
       <c r="J119" t="n">
-        <v>0.098</v>
+        <v>0.096</v>
       </c>
       <c r="K119" t="n">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="L119" t="n">
-        <v>3394</v>
+        <v>3374</v>
       </c>
       <c r="M119" t="inlineStr"/>
     </row>
@@ -5350,19 +5350,19 @@
         <v>0</v>
       </c>
       <c r="H120" t="n">
-        <v>21114</v>
+        <v>21006</v>
       </c>
       <c r="I120" t="n">
-        <v>1.83</v>
+        <v>1.82</v>
       </c>
       <c r="J120" t="n">
-        <v>0.106</v>
+        <v>0.103</v>
       </c>
       <c r="K120" t="n">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="L120" t="n">
-        <v>3475</v>
+        <v>3457</v>
       </c>
       <c r="M120" t="inlineStr"/>
     </row>
@@ -5391,19 +5391,19 @@
         <v>0</v>
       </c>
       <c r="H121" t="n">
-        <v>15574</v>
+        <v>15529</v>
       </c>
       <c r="I121" t="n">
-        <v>0.31</v>
+        <v>0.3</v>
       </c>
       <c r="J121" t="n">
-        <v>0.108</v>
+        <v>0.105</v>
       </c>
       <c r="K121" t="n">
         <v>12</v>
       </c>
       <c r="L121" t="n">
-        <v>3557</v>
+        <v>3537</v>
       </c>
       <c r="M121" t="inlineStr"/>
     </row>
@@ -5429,22 +5429,22 @@
         <v>5.7</v>
       </c>
       <c r="G122" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H122" t="n">
-        <v>94008</v>
+        <v>93795</v>
       </c>
       <c r="I122" t="n">
-        <v>18.25</v>
+        <v>18.19</v>
       </c>
       <c r="J122" t="n">
         <v>0.083</v>
       </c>
       <c r="K122" t="n">
-        <v>1200</v>
+        <v>1199</v>
       </c>
       <c r="L122" t="n">
-        <v>945</v>
+        <v>941</v>
       </c>
       <c r="M122" t="inlineStr"/>
     </row>
@@ -5470,22 +5470,22 @@
         <v>3</v>
       </c>
       <c r="G123" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H123" t="n">
-        <v>54841</v>
+        <v>54692</v>
       </c>
       <c r="I123" t="n">
-        <v>9.9</v>
+        <v>9.859999999999999</v>
       </c>
       <c r="J123" t="n">
         <v>0.091</v>
       </c>
       <c r="K123" t="n">
-        <v>567</v>
+        <v>565</v>
       </c>
       <c r="L123" t="n">
-        <v>1974</v>
+        <v>1966</v>
       </c>
       <c r="M123" t="inlineStr"/>
     </row>
@@ -5514,19 +5514,19 @@
         <v>0</v>
       </c>
       <c r="H124" t="n">
-        <v>29521</v>
+        <v>29597</v>
       </c>
       <c r="I124" t="n">
         <v>4.01</v>
       </c>
       <c r="J124" t="n">
-        <v>0.101</v>
+        <v>0.1</v>
       </c>
       <c r="K124" t="n">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="L124" t="n">
-        <v>2780</v>
+        <v>2765</v>
       </c>
       <c r="M124" t="inlineStr"/>
     </row>
@@ -5552,22 +5552,22 @@
         <v>3.4</v>
       </c>
       <c r="G125" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H125" t="n">
-        <v>61018</v>
+        <v>60980</v>
       </c>
       <c r="I125" t="n">
-        <v>11.02</v>
+        <v>11.03</v>
       </c>
       <c r="J125" t="n">
-        <v>0.091</v>
+        <v>0.09</v>
       </c>
       <c r="K125" t="n">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="L125" t="n">
-        <v>562</v>
+        <v>557</v>
       </c>
       <c r="M125" t="inlineStr"/>
     </row>
@@ -5596,19 +5596,19 @@
         <v>0</v>
       </c>
       <c r="H126" t="n">
-        <v>29713</v>
+        <v>29733</v>
       </c>
       <c r="I126" t="n">
-        <v>4.34</v>
+        <v>4.35</v>
       </c>
       <c r="J126" t="n">
-        <v>0.1</v>
+        <v>0.099</v>
       </c>
       <c r="K126" t="n">
         <v>234</v>
       </c>
       <c r="L126" t="n">
-        <v>994</v>
+        <v>986</v>
       </c>
       <c r="M126" t="inlineStr"/>
     </row>
@@ -5637,19 +5637,19 @@
         <v>0</v>
       </c>
       <c r="H127" t="n">
-        <v>17364</v>
+        <v>17350</v>
       </c>
       <c r="I127" t="n">
         <v>1.25</v>
       </c>
       <c r="J127" t="n">
-        <v>0.107</v>
+        <v>0.104</v>
       </c>
       <c r="K127" t="n">
         <v>54</v>
       </c>
       <c r="L127" t="n">
-        <v>1327</v>
+        <v>1324</v>
       </c>
       <c r="M127" t="inlineStr"/>
     </row>
@@ -5678,19 +5678,19 @@
         <v>0</v>
       </c>
       <c r="H128" t="n">
-        <v>46904</v>
+        <v>46916</v>
       </c>
       <c r="I128" t="n">
-        <v>7.61</v>
+        <v>7.62</v>
       </c>
       <c r="J128" t="n">
-        <v>0.098</v>
+        <v>0.096</v>
       </c>
       <c r="K128" t="n">
         <v>561</v>
       </c>
       <c r="L128" t="n">
-        <v>536</v>
+        <v>531</v>
       </c>
       <c r="M128" t="inlineStr"/>
     </row>
@@ -5719,19 +5719,19 @@
         <v>0</v>
       </c>
       <c r="H129" t="n">
-        <v>19851</v>
+        <v>19789</v>
       </c>
       <c r="I129" t="n">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="J129" t="n">
-        <v>0.106</v>
+        <v>0.103</v>
       </c>
       <c r="K129" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="L129" t="n">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="M129" t="inlineStr"/>
     </row>
@@ -5760,19 +5760,19 @@
         <v>0</v>
       </c>
       <c r="H130" t="n">
-        <v>13842</v>
+        <v>13820</v>
       </c>
       <c r="I130" t="n">
-        <v>0.34</v>
+        <v>0.33</v>
       </c>
       <c r="J130" t="n">
-        <v>0.107</v>
+        <v>0.105</v>
       </c>
       <c r="K130" t="n">
         <v>15</v>
       </c>
       <c r="L130" t="n">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="M130" t="inlineStr"/>
     </row>
@@ -5801,19 +5801,19 @@
         <v>0</v>
       </c>
       <c r="H131" t="n">
-        <v>43740</v>
+        <v>43754</v>
       </c>
       <c r="I131" t="n">
-        <v>6.63</v>
+        <v>6.64</v>
       </c>
       <c r="J131" t="n">
-        <v>0.099</v>
+        <v>0.097</v>
       </c>
       <c r="K131" t="n">
         <v>523</v>
       </c>
       <c r="L131" t="n">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="M131" t="inlineStr"/>
     </row>
@@ -5842,19 +5842,19 @@
         <v>0</v>
       </c>
       <c r="H132" t="n">
-        <v>17717</v>
+        <v>17662</v>
       </c>
       <c r="I132" t="n">
         <v>1.27</v>
       </c>
       <c r="J132" t="n">
-        <v>0.106</v>
+        <v>0.104</v>
       </c>
       <c r="K132" t="n">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="L132" t="n">
-        <v>608</v>
+        <v>603</v>
       </c>
       <c r="M132" t="inlineStr"/>
     </row>
@@ -5883,19 +5883,19 @@
         <v>0</v>
       </c>
       <c r="H133" t="n">
-        <v>13498</v>
+        <v>13493</v>
       </c>
       <c r="I133" t="n">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="J133" t="n">
-        <v>0.108</v>
+        <v>0.106</v>
       </c>
       <c r="K133" t="n">
         <v>5</v>
       </c>
       <c r="L133" t="n">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="M133" t="inlineStr"/>
     </row>
@@ -5924,19 +5924,19 @@
         <v>0</v>
       </c>
       <c r="H134" t="n">
-        <v>43691</v>
+        <v>43690</v>
       </c>
       <c r="I134" t="n">
         <v>6.43</v>
       </c>
       <c r="J134" t="n">
-        <v>0.099</v>
+        <v>0.098</v>
       </c>
       <c r="K134" t="n">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="L134" t="n">
-        <v>607</v>
+        <v>600</v>
       </c>
       <c r="M134" t="inlineStr"/>
     </row>
@@ -5965,19 +5965,19 @@
         <v>0</v>
       </c>
       <c r="H135" t="n">
-        <v>17830</v>
+        <v>17794</v>
       </c>
       <c r="I135" t="n">
         <v>1.13</v>
       </c>
       <c r="J135" t="n">
-        <v>0.107</v>
+        <v>0.104</v>
       </c>
       <c r="K135" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="L135" t="n">
-        <v>610</v>
+        <v>603</v>
       </c>
       <c r="M135" t="inlineStr"/>
     </row>
@@ -6006,19 +6006,19 @@
         <v>0</v>
       </c>
       <c r="H136" t="n">
-        <v>13993</v>
+        <v>14001</v>
       </c>
       <c r="I136" t="n">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="J136" t="n">
-        <v>0.108</v>
+        <v>0.106</v>
       </c>
       <c r="K136" t="n">
         <v>3</v>
       </c>
       <c r="L136" t="n">
-        <v>614</v>
+        <v>607</v>
       </c>
       <c r="M136" t="inlineStr"/>
     </row>
@@ -6047,19 +6047,19 @@
         <v>0</v>
       </c>
       <c r="H137" t="n">
-        <v>85975</v>
+        <v>85836</v>
       </c>
       <c r="I137" t="n">
-        <v>15.83</v>
+        <v>15.8</v>
       </c>
       <c r="J137" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="K137" t="n">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="L137" t="n">
-        <v>782</v>
+        <v>776</v>
       </c>
       <c r="M137" t="inlineStr"/>
     </row>
@@ -6088,19 +6088,19 @@
         <v>0</v>
       </c>
       <c r="H138" t="n">
-        <v>47249</v>
+        <v>47200</v>
       </c>
       <c r="I138" t="n">
-        <v>7.71</v>
+        <v>7.7</v>
       </c>
       <c r="J138" t="n">
-        <v>0.093</v>
+        <v>0.092</v>
       </c>
       <c r="K138" t="n">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="L138" t="n">
-        <v>1726</v>
+        <v>1718</v>
       </c>
       <c r="M138" t="inlineStr"/>
     </row>
@@ -6129,19 +6129,19 @@
         <v>0</v>
       </c>
       <c r="H139" t="n">
-        <v>23849</v>
+        <v>23940</v>
       </c>
       <c r="I139" t="n">
-        <v>2.38</v>
+        <v>2.39</v>
       </c>
       <c r="J139" t="n">
-        <v>0.104</v>
+        <v>0.102</v>
       </c>
       <c r="K139" t="n">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="L139" t="n">
-        <v>2400</v>
+        <v>2390</v>
       </c>
       <c r="M139" t="inlineStr"/>
     </row>
@@ -6170,19 +6170,19 @@
         <v>0</v>
       </c>
       <c r="H140" t="n">
-        <v>54317</v>
+        <v>54340</v>
       </c>
       <c r="I140" t="n">
-        <v>9.08</v>
+        <v>9.1</v>
       </c>
       <c r="J140" t="n">
-        <v>0.094</v>
+        <v>0.093</v>
       </c>
       <c r="K140" t="n">
-        <v>676</v>
+        <v>673</v>
       </c>
       <c r="L140" t="n">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="M140" t="inlineStr"/>
     </row>
@@ -6211,19 +6211,19 @@
         <v>0</v>
       </c>
       <c r="H141" t="n">
-        <v>24221</v>
+        <v>24267</v>
       </c>
       <c r="I141" t="n">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="J141" t="n">
-        <v>0.103</v>
+        <v>0.101</v>
       </c>
       <c r="K141" t="n">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="L141" t="n">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="M141" t="inlineStr"/>
     </row>
@@ -6252,19 +6252,19 @@
         <v>0</v>
       </c>
       <c r="H142" t="n">
-        <v>14673</v>
+        <v>14680</v>
       </c>
       <c r="I142" t="n">
         <v>0.44</v>
       </c>
       <c r="J142" t="n">
-        <v>0.107</v>
+        <v>0.105</v>
       </c>
       <c r="K142" t="n">
         <v>24</v>
       </c>
       <c r="L142" t="n">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="M142" t="inlineStr"/>
     </row>
@@ -6293,16 +6293,16 @@
         <v>0</v>
       </c>
       <c r="H143" t="n">
-        <v>43984</v>
+        <v>44005</v>
       </c>
       <c r="I143" t="n">
-        <v>6.67</v>
+        <v>6.68</v>
       </c>
       <c r="J143" t="n">
-        <v>0.099</v>
+        <v>0.097</v>
       </c>
       <c r="K143" t="n">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="L143" t="n">
         <v>38</v>
@@ -6334,19 +6334,19 @@
         <v>0</v>
       </c>
       <c r="H144" t="n">
-        <v>17726</v>
+        <v>17698</v>
       </c>
       <c r="I144" t="n">
         <v>1.27</v>
       </c>
       <c r="J144" t="n">
-        <v>0.106</v>
+        <v>0.104</v>
       </c>
       <c r="K144" t="n">
         <v>83</v>
       </c>
       <c r="L144" t="n">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="M144" t="inlineStr"/>
     </row>
@@ -6375,19 +6375,19 @@
         <v>0</v>
       </c>
       <c r="H145" t="n">
-        <v>13348</v>
+        <v>13371</v>
       </c>
       <c r="I145" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="J145" t="n">
-        <v>0.108</v>
+        <v>0.106</v>
       </c>
       <c r="K145" t="n">
         <v>4</v>
       </c>
       <c r="L145" t="n">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="M145" t="inlineStr">
         <is>
@@ -6420,16 +6420,16 @@
         <v>0</v>
       </c>
       <c r="H146" t="n">
-        <v>43539</v>
+        <v>43537</v>
       </c>
       <c r="I146" t="n">
         <v>6.4</v>
       </c>
       <c r="J146" t="n">
-        <v>0.099</v>
+        <v>0.098</v>
       </c>
       <c r="K146" t="n">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="L146" t="n">
         <v>22</v>
@@ -6461,16 +6461,16 @@
         <v>0</v>
       </c>
       <c r="H147" t="n">
-        <v>17698</v>
+        <v>17661</v>
       </c>
       <c r="I147" t="n">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="J147" t="n">
-        <v>0.107</v>
+        <v>0.104</v>
       </c>
       <c r="K147" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L147" t="n">
         <v>23</v>
@@ -6502,13 +6502,13 @@
         <v>0</v>
       </c>
       <c r="H148" t="n">
-        <v>13917</v>
+        <v>13915</v>
       </c>
       <c r="I148" t="n">
         <v>0.04</v>
       </c>
       <c r="J148" t="n">
-        <v>0.108</v>
+        <v>0.106</v>
       </c>
       <c r="K148" t="n">
         <v>2</v>
@@ -6543,19 +6543,19 @@
         <v>0</v>
       </c>
       <c r="H149" t="n">
-        <v>44230</v>
+        <v>44215</v>
       </c>
       <c r="I149" t="n">
         <v>6.39</v>
       </c>
       <c r="J149" t="n">
-        <v>0.099</v>
+        <v>0.098</v>
       </c>
       <c r="K149" t="n">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="L149" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M149" t="inlineStr"/>
     </row>
@@ -6584,19 +6584,19 @@
         <v>0</v>
       </c>
       <c r="H150" t="n">
-        <v>18399</v>
+        <v>18351</v>
       </c>
       <c r="I150" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="J150" t="n">
-        <v>0.107</v>
+        <v>0.104</v>
       </c>
       <c r="K150" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L150" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="M150" t="inlineStr"/>
     </row>
@@ -6625,13 +6625,13 @@
         <v>0</v>
       </c>
       <c r="H151" t="n">
-        <v>14641</v>
+        <v>14634</v>
       </c>
       <c r="I151" t="n">
         <v>0.04</v>
       </c>
       <c r="J151" t="n">
-        <v>0.108</v>
+        <v>0.106</v>
       </c>
       <c r="K151" t="n">
         <v>2</v>
@@ -6666,19 +6666,19 @@
         <v>0</v>
       </c>
       <c r="H152" t="n">
-        <v>86627</v>
+        <v>86502</v>
       </c>
       <c r="I152" t="n">
-        <v>15.74</v>
+        <v>15.71</v>
       </c>
       <c r="J152" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="K152" t="n">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="L152" t="n">
-        <v>776</v>
+        <v>770</v>
       </c>
       <c r="M152" t="inlineStr"/>
     </row>
@@ -6707,10 +6707,10 @@
         <v>0</v>
       </c>
       <c r="H153" t="n">
-        <v>47942</v>
+        <v>47898</v>
       </c>
       <c r="I153" t="n">
-        <v>7.63</v>
+        <v>7.62</v>
       </c>
       <c r="J153" t="n">
         <v>0.093</v>
@@ -6719,7 +6719,7 @@
         <v>495</v>
       </c>
       <c r="L153" t="n">
-        <v>1716</v>
+        <v>1709</v>
       </c>
       <c r="M153" t="inlineStr"/>
     </row>
@@ -6742,25 +6742,25 @@
         <v>70</v>
       </c>
       <c r="F154" t="n">
-        <v>1.2</v>
+        <v>1.3</v>
       </c>
       <c r="G154" t="n">
         <v>0</v>
       </c>
       <c r="H154" t="n">
-        <v>24574</v>
+        <v>24683</v>
       </c>
       <c r="I154" t="n">
-        <v>2.31</v>
+        <v>2.33</v>
       </c>
       <c r="J154" t="n">
-        <v>0.104</v>
+        <v>0.102</v>
       </c>
       <c r="K154" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="L154" t="n">
-        <v>2388</v>
+        <v>2377</v>
       </c>
       <c r="M154" t="inlineStr"/>
     </row>
@@ -6789,19 +6789,19 @@
         <v>0</v>
       </c>
       <c r="H155" t="n">
-        <v>55013</v>
+        <v>55046</v>
       </c>
       <c r="I155" t="n">
-        <v>9</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="J155" t="n">
-        <v>0.094</v>
+        <v>0.093</v>
       </c>
       <c r="K155" t="n">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="L155" t="n">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="M155" t="inlineStr"/>
     </row>
@@ -6830,19 +6830,19 @@
         <v>0</v>
       </c>
       <c r="H156" t="n">
-        <v>24954</v>
+        <v>25025</v>
       </c>
       <c r="I156" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="J156" t="n">
-        <v>0.103</v>
+        <v>0.101</v>
       </c>
       <c r="K156" t="n">
         <v>174</v>
       </c>
       <c r="L156" t="n">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="M156" t="inlineStr"/>
     </row>
@@ -6871,19 +6871,19 @@
         <v>0</v>
       </c>
       <c r="H157" t="n">
-        <v>15504</v>
+        <v>15528</v>
       </c>
       <c r="I157" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="J157" t="n">
-        <v>0.107</v>
+        <v>0.105</v>
       </c>
       <c r="K157" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L157" t="n">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="M157" t="inlineStr"/>
     </row>
@@ -6912,19 +6912,19 @@
         <v>0</v>
       </c>
       <c r="H158" t="n">
-        <v>44810</v>
+        <v>44849</v>
       </c>
       <c r="I158" t="n">
-        <v>6.63</v>
+        <v>6.65</v>
       </c>
       <c r="J158" t="n">
-        <v>0.099</v>
+        <v>0.097</v>
       </c>
       <c r="K158" t="n">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="L158" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M158" t="inlineStr"/>
     </row>
@@ -6953,19 +6953,19 @@
         <v>0</v>
       </c>
       <c r="H159" t="n">
-        <v>18583</v>
+        <v>18566</v>
       </c>
       <c r="I159" t="n">
         <v>1.24</v>
       </c>
       <c r="J159" t="n">
-        <v>0.106</v>
+        <v>0.104</v>
       </c>
       <c r="K159" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L159" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M159" t="inlineStr"/>
     </row>
@@ -6994,19 +6994,19 @@
         <v>0</v>
       </c>
       <c r="H160" t="n">
-        <v>14282</v>
+        <v>14302</v>
       </c>
       <c r="I160" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J160" t="n">
-        <v>0.108</v>
+        <v>0.106</v>
       </c>
       <c r="K160" t="n">
         <v>4</v>
       </c>
       <c r="L160" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="M160" t="inlineStr"/>
     </row>
@@ -7035,19 +7035,19 @@
         <v>0</v>
       </c>
       <c r="H161" t="n">
-        <v>44493</v>
+        <v>44482</v>
       </c>
       <c r="I161" t="n">
-        <v>6.39</v>
+        <v>6.4</v>
       </c>
       <c r="J161" t="n">
-        <v>0.099</v>
+        <v>0.098</v>
       </c>
       <c r="K161" t="n">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="L161" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M161" t="inlineStr"/>
     </row>
@@ -7076,19 +7076,19 @@
         <v>0</v>
       </c>
       <c r="H162" t="n">
-        <v>18659</v>
+        <v>18612</v>
       </c>
       <c r="I162" t="n">
         <v>1.1</v>
       </c>
       <c r="J162" t="n">
-        <v>0.107</v>
+        <v>0.104</v>
       </c>
       <c r="K162" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M162" t="inlineStr"/>
     </row>
@@ -7117,19 +7117,19 @@
         <v>0</v>
       </c>
       <c r="H163" t="n">
-        <v>14888</v>
+        <v>14881</v>
       </c>
       <c r="I163" t="n">
         <v>0.04</v>
       </c>
       <c r="J163" t="n">
-        <v>0.108</v>
+        <v>0.106</v>
       </c>
       <c r="K163" t="n">
         <v>2</v>
       </c>
       <c r="L163" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M163" t="inlineStr"/>
     </row>
@@ -7158,16 +7158,16 @@
         <v>0</v>
       </c>
       <c r="H164" t="n">
-        <v>45205</v>
+        <v>45188</v>
       </c>
       <c r="I164" t="n">
         <v>6.39</v>
       </c>
       <c r="J164" t="n">
-        <v>0.099</v>
+        <v>0.098</v>
       </c>
       <c r="K164" t="n">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="L164" t="n">
         <v>0</v>
@@ -7199,16 +7199,16 @@
         <v>0</v>
       </c>
       <c r="H165" t="n">
-        <v>19373</v>
+        <v>19324</v>
       </c>
       <c r="I165" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="J165" t="n">
-        <v>0.107</v>
+        <v>0.104</v>
       </c>
       <c r="K165" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L165" t="n">
         <v>0</v>
@@ -7240,13 +7240,13 @@
         <v>0</v>
       </c>
       <c r="H166" t="n">
-        <v>15615</v>
+        <v>15608</v>
       </c>
       <c r="I166" t="n">
         <v>0.04</v>
       </c>
       <c r="J166" t="n">
-        <v>0.108</v>
+        <v>0.106</v>
       </c>
       <c r="K166" t="n">
         <v>2</v>
@@ -7275,25 +7275,25 @@
         <v>70</v>
       </c>
       <c r="F167" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
       </c>
       <c r="H167" t="n">
-        <v>87613</v>
+        <v>87484</v>
       </c>
       <c r="I167" t="n">
-        <v>15.74</v>
+        <v>15.71</v>
       </c>
       <c r="J167" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="K167" t="n">
-        <v>1135</v>
+        <v>1133</v>
       </c>
       <c r="L167" t="n">
-        <v>776</v>
+        <v>770</v>
       </c>
       <c r="M167" t="inlineStr"/>
     </row>
@@ -7322,19 +7322,19 @@
         <v>0</v>
       </c>
       <c r="H168" t="n">
-        <v>48928</v>
+        <v>48880</v>
       </c>
       <c r="I168" t="n">
-        <v>7.63</v>
+        <v>7.62</v>
       </c>
       <c r="J168" t="n">
         <v>0.093</v>
       </c>
       <c r="K168" t="n">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="L168" t="n">
-        <v>1716</v>
+        <v>1709</v>
       </c>
       <c r="M168" t="inlineStr"/>
     </row>
@@ -7363,19 +7363,19 @@
         <v>0</v>
       </c>
       <c r="H169" t="n">
-        <v>25560</v>
+        <v>25665</v>
       </c>
       <c r="I169" t="n">
-        <v>2.31</v>
+        <v>2.32</v>
       </c>
       <c r="J169" t="n">
-        <v>0.104</v>
+        <v>0.102</v>
       </c>
       <c r="K169" t="n">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="L169" t="n">
-        <v>2388</v>
+        <v>2377</v>
       </c>
       <c r="M169" t="inlineStr"/>
     </row>
@@ -7404,19 +7404,19 @@
         <v>0</v>
       </c>
       <c r="H170" t="n">
-        <v>55998</v>
+        <v>56027</v>
       </c>
       <c r="I170" t="n">
-        <v>9</v>
+        <v>9.029999999999999</v>
       </c>
       <c r="J170" t="n">
-        <v>0.094</v>
+        <v>0.093</v>
       </c>
       <c r="K170" t="n">
-        <v>674</v>
+        <v>671</v>
       </c>
       <c r="L170" t="n">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="M170" t="inlineStr"/>
     </row>
@@ -7445,19 +7445,19 @@
         <v>0</v>
       </c>
       <c r="H171" t="n">
-        <v>25940</v>
+        <v>26007</v>
       </c>
       <c r="I171" t="n">
-        <v>2.72</v>
+        <v>2.74</v>
       </c>
       <c r="J171" t="n">
-        <v>0.103</v>
+        <v>0.101</v>
       </c>
       <c r="K171" t="n">
         <v>174</v>
       </c>
       <c r="L171" t="n">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="M171" t="inlineStr"/>
     </row>
@@ -7486,19 +7486,19 @@
         <v>0</v>
       </c>
       <c r="H172" t="n">
-        <v>16490</v>
+        <v>16510</v>
       </c>
       <c r="I172" t="n">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="J172" t="n">
-        <v>0.107</v>
+        <v>0.105</v>
       </c>
       <c r="K172" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="L172" t="n">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="M172" t="inlineStr"/>
     </row>
@@ -7527,19 +7527,19 @@
         <v>0</v>
       </c>
       <c r="H173" t="n">
-        <v>45796</v>
+        <v>45831</v>
       </c>
       <c r="I173" t="n">
-        <v>6.63</v>
+        <v>6.65</v>
       </c>
       <c r="J173" t="n">
-        <v>0.099</v>
+        <v>0.097</v>
       </c>
       <c r="K173" t="n">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="L173" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="M173" t="inlineStr"/>
     </row>
@@ -7568,19 +7568,19 @@
         <v>0</v>
       </c>
       <c r="H174" t="n">
-        <v>19568</v>
+        <v>19550</v>
       </c>
       <c r="I174" t="n">
         <v>1.24</v>
       </c>
       <c r="J174" t="n">
-        <v>0.106</v>
+        <v>0.104</v>
       </c>
       <c r="K174" t="n">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="L174" t="n">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="M174" t="inlineStr"/>
     </row>
@@ -7609,19 +7609,19 @@
         <v>0</v>
       </c>
       <c r="H175" t="n">
-        <v>15267</v>
+        <v>15287</v>
       </c>
       <c r="I175" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J175" t="n">
-        <v>0.108</v>
+        <v>0.106</v>
       </c>
       <c r="K175" t="n">
         <v>4</v>
       </c>
       <c r="L175" t="n">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="M175" t="inlineStr"/>
     </row>
@@ -7650,16 +7650,16 @@
         <v>0</v>
       </c>
       <c r="H176" t="n">
-        <v>45479</v>
+        <v>45467</v>
       </c>
       <c r="I176" t="n">
-        <v>6.39</v>
+        <v>6.4</v>
       </c>
       <c r="J176" t="n">
-        <v>0.099</v>
+        <v>0.098</v>
       </c>
       <c r="K176" t="n">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="L176" t="n">
         <v>0</v>
@@ -7691,19 +7691,19 @@
         <v>0</v>
       </c>
       <c r="H177" t="n">
-        <v>19645</v>
+        <v>19597</v>
       </c>
       <c r="I177" t="n">
         <v>1.1</v>
       </c>
       <c r="J177" t="n">
-        <v>0.107</v>
+        <v>0.104</v>
       </c>
       <c r="K177" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L177" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M177" t="inlineStr"/>
     </row>
@@ -7732,19 +7732,19 @@
         <v>0</v>
       </c>
       <c r="H178" t="n">
-        <v>15874</v>
+        <v>15867</v>
       </c>
       <c r="I178" t="n">
         <v>0.04</v>
       </c>
       <c r="J178" t="n">
-        <v>0.108</v>
+        <v>0.106</v>
       </c>
       <c r="K178" t="n">
         <v>2</v>
       </c>
       <c r="L178" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M178" t="inlineStr"/>
     </row>
@@ -7773,16 +7773,16 @@
         <v>0</v>
       </c>
       <c r="H179" t="n">
-        <v>46190</v>
+        <v>46173</v>
       </c>
       <c r="I179" t="n">
         <v>6.39</v>
       </c>
       <c r="J179" t="n">
-        <v>0.099</v>
+        <v>0.098</v>
       </c>
       <c r="K179" t="n">
-        <v>516</v>
+        <v>514</v>
       </c>
       <c r="L179" t="n">
         <v>0</v>
@@ -7814,16 +7814,16 @@
         <v>0</v>
       </c>
       <c r="H180" t="n">
-        <v>20359</v>
+        <v>20309</v>
       </c>
       <c r="I180" t="n">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="J180" t="n">
-        <v>0.107</v>
+        <v>0.104</v>
       </c>
       <c r="K180" t="n">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="L180" t="n">
         <v>0</v>
@@ -7855,13 +7855,13 @@
         <v>0</v>
       </c>
       <c r="H181" t="n">
-        <v>16601</v>
+        <v>16594</v>
       </c>
       <c r="I181" t="n">
         <v>0.04</v>
       </c>
       <c r="J181" t="n">
-        <v>0.108</v>
+        <v>0.106</v>
       </c>
       <c r="K181" t="n">
         <v>2</v>
@@ -7893,19 +7893,19 @@
         <v>31.6</v>
       </c>
       <c r="G182" t="n">
-        <v>0.3</v>
+        <v>0.2</v>
       </c>
       <c r="H182" t="n">
-        <v>346815</v>
+        <v>346468</v>
       </c>
       <c r="I182" t="n">
-        <v>62.23</v>
+        <v>62.22</v>
       </c>
       <c r="J182" t="n">
-        <v>0.042</v>
+        <v>0.04</v>
       </c>
       <c r="K182" t="n">
-        <v>2657</v>
+        <v>2651</v>
       </c>
       <c r="L182" t="n">
         <v>3312</v>
@@ -7934,22 +7934,22 @@
         <v>21.9</v>
       </c>
       <c r="G183" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="H183" t="n">
-        <v>297894</v>
+        <v>297634</v>
       </c>
       <c r="I183" t="n">
-        <v>53.2</v>
+        <v>53.17</v>
       </c>
       <c r="J183" t="n">
-        <v>0.054</v>
+        <v>0.051</v>
       </c>
       <c r="K183" t="n">
         <v>2157</v>
       </c>
       <c r="L183" t="n">
-        <v>5378</v>
+        <v>5379</v>
       </c>
       <c r="M183" t="inlineStr"/>
     </row>
@@ -7978,16 +7978,16 @@
         <v>0.1</v>
       </c>
       <c r="H184" t="n">
-        <v>251488</v>
+        <v>251201</v>
       </c>
       <c r="I184" t="n">
-        <v>44.34</v>
+        <v>44.29</v>
       </c>
       <c r="J184" t="n">
-        <v>0.063</v>
+        <v>0.059</v>
       </c>
       <c r="K184" t="n">
-        <v>1727</v>
+        <v>1729</v>
       </c>
       <c r="L184" t="n">
         <v>7475</v>
@@ -8016,22 +8016,22 @@
         <v>21.9</v>
       </c>
       <c r="G185" t="n">
-        <v>0.2</v>
+        <v>0.1</v>
       </c>
       <c r="H185" t="n">
-        <v>298144</v>
+        <v>298044</v>
       </c>
       <c r="I185" t="n">
         <v>53.1</v>
       </c>
       <c r="J185" t="n">
-        <v>0.055</v>
+        <v>0.051</v>
       </c>
       <c r="K185" t="n">
-        <v>2254</v>
+        <v>2255</v>
       </c>
       <c r="L185" t="n">
-        <v>4605</v>
+        <v>4606</v>
       </c>
       <c r="M185" t="inlineStr"/>
     </row>
@@ -8060,19 +8060,19 @@
         <v>0.1</v>
       </c>
       <c r="H186" t="n">
-        <v>250752</v>
+        <v>250523</v>
       </c>
       <c r="I186" t="n">
-        <v>44.27</v>
+        <v>44.24</v>
       </c>
       <c r="J186" t="n">
-        <v>0.062</v>
+        <v>0.06</v>
       </c>
       <c r="K186" t="n">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="L186" t="n">
-        <v>6433</v>
+        <v>6438</v>
       </c>
       <c r="M186" t="inlineStr"/>
     </row>
@@ -8101,19 +8101,19 @@
         <v>0.1</v>
       </c>
       <c r="H187" t="n">
-        <v>206085</v>
+        <v>205922</v>
       </c>
       <c r="I187" t="n">
-        <v>35.7</v>
+        <v>35.68</v>
       </c>
       <c r="J187" t="n">
-        <v>0.07000000000000001</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="K187" t="n">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="L187" t="n">
-        <v>8357</v>
+        <v>8349</v>
       </c>
       <c r="M187" t="inlineStr"/>
     </row>
@@ -8142,16 +8142,16 @@
         <v>0.1</v>
       </c>
       <c r="H188" t="n">
-        <v>252393</v>
+        <v>252099</v>
       </c>
       <c r="I188" t="n">
-        <v>44.29</v>
+        <v>44.28</v>
       </c>
       <c r="J188" t="n">
-        <v>0.064</v>
+        <v>0.06</v>
       </c>
       <c r="K188" t="n">
-        <v>1911</v>
+        <v>1905</v>
       </c>
       <c r="L188" t="n">
         <v>5974</v>
@@ -8183,19 +8183,19 @@
         <v>0.1</v>
       </c>
       <c r="H189" t="n">
-        <v>206013</v>
+        <v>205849</v>
       </c>
       <c r="I189" t="n">
         <v>35.71</v>
       </c>
       <c r="J189" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.068</v>
       </c>
       <c r="K189" t="n">
-        <v>1451</v>
+        <v>1448</v>
       </c>
       <c r="L189" t="n">
-        <v>7518</v>
+        <v>7514</v>
       </c>
       <c r="M189" t="inlineStr"/>
     </row>
@@ -8224,19 +8224,19 @@
         <v>0.1</v>
       </c>
       <c r="H190" t="n">
-        <v>163654</v>
+        <v>163490</v>
       </c>
       <c r="I190" t="n">
-        <v>27.6</v>
+        <v>27.58</v>
       </c>
       <c r="J190" t="n">
-        <v>0.078</v>
+        <v>0.076</v>
       </c>
       <c r="K190" t="n">
         <v>1065</v>
       </c>
       <c r="L190" t="n">
-        <v>9217</v>
+        <v>9210</v>
       </c>
       <c r="M190" t="inlineStr"/>
     </row>
@@ -8265,19 +8265,19 @@
         <v>0.1</v>
       </c>
       <c r="H191" t="n">
-        <v>209511</v>
+        <v>209321</v>
       </c>
       <c r="I191" t="n">
-        <v>35.98</v>
+        <v>35.99</v>
       </c>
       <c r="J191" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.068</v>
       </c>
       <c r="K191" t="n">
-        <v>1595</v>
+        <v>1590</v>
       </c>
       <c r="L191" t="n">
-        <v>7317</v>
+        <v>7313</v>
       </c>
       <c r="M191" t="inlineStr"/>
     </row>
@@ -8306,19 +8306,19 @@
         <v>0.1</v>
       </c>
       <c r="H192" t="n">
-        <v>164434</v>
+        <v>164311</v>
       </c>
       <c r="I192" t="n">
-        <v>27.74</v>
+        <v>27.75</v>
       </c>
       <c r="J192" t="n">
-        <v>0.078</v>
+        <v>0.076</v>
       </c>
       <c r="K192" t="n">
-        <v>1140</v>
+        <v>1136</v>
       </c>
       <c r="L192" t="n">
-        <v>8559</v>
+        <v>8553</v>
       </c>
       <c r="M192" t="inlineStr"/>
     </row>
@@ -8344,22 +8344,22 @@
         <v>5.4</v>
       </c>
       <c r="G193" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H193" t="n">
-        <v>125010</v>
+        <v>124891</v>
       </c>
       <c r="I193" t="n">
-        <v>20.18</v>
+        <v>20.17</v>
       </c>
       <c r="J193" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="K193" t="n">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="L193" t="n">
-        <v>9974</v>
+        <v>9963</v>
       </c>
       <c r="M193" t="inlineStr"/>
     </row>
@@ -8388,19 +8388,19 @@
         <v>0.1</v>
       </c>
       <c r="H194" t="n">
-        <v>171214</v>
+        <v>170988</v>
       </c>
       <c r="I194" t="n">
         <v>28.43</v>
       </c>
       <c r="J194" t="n">
-        <v>0.082</v>
+        <v>0.078</v>
       </c>
       <c r="K194" t="n">
-        <v>1333</v>
+        <v>1327</v>
       </c>
       <c r="L194" t="n">
-        <v>8559</v>
+        <v>8554</v>
       </c>
       <c r="M194" t="inlineStr"/>
     </row>
@@ -8426,22 +8426,22 @@
         <v>5.5</v>
       </c>
       <c r="G195" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H195" t="n">
-        <v>127581</v>
+        <v>127391</v>
       </c>
       <c r="I195" t="n">
-        <v>20.58</v>
+        <v>20.59</v>
       </c>
       <c r="J195" t="n">
-        <v>0.09</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="K195" t="n">
-        <v>878</v>
+        <v>872</v>
       </c>
       <c r="L195" t="n">
-        <v>9470</v>
+        <v>9456</v>
       </c>
       <c r="M195" t="inlineStr"/>
     </row>
@@ -8464,25 +8464,25 @@
         <v>50</v>
       </c>
       <c r="F196" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="G196" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H196" t="n">
-        <v>91554</v>
+        <v>91482</v>
       </c>
       <c r="I196" t="n">
         <v>13.74</v>
       </c>
       <c r="J196" t="n">
-        <v>0.095</v>
+        <v>0.094</v>
       </c>
       <c r="K196" t="n">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="L196" t="n">
-        <v>10579</v>
+        <v>10562</v>
       </c>
       <c r="M196" t="inlineStr"/>
     </row>
@@ -8511,19 +8511,19 @@
         <v>0.1</v>
       </c>
       <c r="H197" t="n">
-        <v>257848</v>
+        <v>257627</v>
       </c>
       <c r="I197" t="n">
-        <v>44.85</v>
+        <v>44.83</v>
       </c>
       <c r="J197" t="n">
-        <v>0.065</v>
+        <v>0.062</v>
       </c>
       <c r="K197" t="n">
-        <v>2127</v>
+        <v>2125</v>
       </c>
       <c r="L197" t="n">
-        <v>2209</v>
+        <v>2212</v>
       </c>
       <c r="M197" t="inlineStr"/>
     </row>
@@ -8546,25 +8546,25 @@
         <v>35</v>
       </c>
       <c r="F198" t="n">
-        <v>11.4</v>
+        <v>11.3</v>
       </c>
       <c r="G198" t="n">
         <v>0.1</v>
       </c>
       <c r="H198" t="n">
-        <v>210278</v>
+        <v>210034</v>
       </c>
       <c r="I198" t="n">
-        <v>36.32</v>
+        <v>36.31</v>
       </c>
       <c r="J198" t="n">
-        <v>0.076</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="K198" t="n">
-        <v>1611</v>
+        <v>1608</v>
       </c>
       <c r="L198" t="n">
-        <v>3865</v>
+        <v>3869</v>
       </c>
       <c r="M198" t="inlineStr"/>
     </row>
@@ -8593,19 +8593,19 @@
         <v>0.1</v>
       </c>
       <c r="H199" t="n">
-        <v>166184</v>
+        <v>165947</v>
       </c>
       <c r="I199" t="n">
-        <v>28.07</v>
+        <v>28.06</v>
       </c>
       <c r="J199" t="n">
-        <v>0.081</v>
+        <v>0.078</v>
       </c>
       <c r="K199" t="n">
-        <v>1184</v>
+        <v>1180</v>
       </c>
       <c r="L199" t="n">
-        <v>5585</v>
+        <v>5583</v>
       </c>
       <c r="M199" t="inlineStr"/>
     </row>
@@ -8634,16 +8634,16 @@
         <v>0.1</v>
       </c>
       <c r="H200" t="n">
-        <v>211898</v>
+        <v>211634</v>
       </c>
       <c r="I200" t="n">
-        <v>36.4</v>
+        <v>36.42</v>
       </c>
       <c r="J200" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.06900000000000001</v>
       </c>
       <c r="K200" t="n">
-        <v>1729</v>
+        <v>1718</v>
       </c>
       <c r="L200" t="n">
         <v>2711</v>
@@ -8669,25 +8669,25 @@
         <v>40</v>
       </c>
       <c r="F201" t="n">
-        <v>8</v>
+        <v>7.9</v>
       </c>
       <c r="G201" t="n">
         <v>0.1</v>
       </c>
       <c r="H201" t="n">
-        <v>166159</v>
+        <v>165910</v>
       </c>
       <c r="I201" t="n">
         <v>28.17</v>
       </c>
       <c r="J201" t="n">
-        <v>0.082</v>
+        <v>0.079</v>
       </c>
       <c r="K201" t="n">
-        <v>1245</v>
+        <v>1238</v>
       </c>
       <c r="L201" t="n">
-        <v>4017</v>
+        <v>4019</v>
       </c>
       <c r="M201" t="inlineStr"/>
     </row>
@@ -8713,22 +8713,22 @@
         <v>5.4</v>
       </c>
       <c r="G202" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H202" t="n">
-        <v>125527</v>
+        <v>125321</v>
       </c>
       <c r="I202" t="n">
-        <v>20.53</v>
+        <v>20.52</v>
       </c>
       <c r="J202" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="K202" t="n">
-        <v>857</v>
+        <v>853</v>
       </c>
       <c r="L202" t="n">
-        <v>5459</v>
+        <v>5461</v>
       </c>
       <c r="M202" t="inlineStr"/>
     </row>
@@ -8757,19 +8757,19 @@
         <v>0.1</v>
       </c>
       <c r="H203" t="n">
-        <v>171347</v>
+        <v>170945</v>
       </c>
       <c r="I203" t="n">
-        <v>28.75</v>
+        <v>28.74</v>
       </c>
       <c r="J203" t="n">
-        <v>0.083</v>
+        <v>0.078</v>
       </c>
       <c r="K203" t="n">
-        <v>1404</v>
+        <v>1394</v>
       </c>
       <c r="L203" t="n">
-        <v>3428</v>
+        <v>3420</v>
       </c>
       <c r="M203" t="inlineStr"/>
     </row>
@@ -8795,22 +8795,22 @@
         <v>5.5</v>
       </c>
       <c r="G204" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H204" t="n">
-        <v>127163</v>
+        <v>126918</v>
       </c>
       <c r="I204" t="n">
-        <v>20.86</v>
+        <v>20.87</v>
       </c>
       <c r="J204" t="n">
-        <v>0.09</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="K204" t="n">
-        <v>933</v>
+        <v>925</v>
       </c>
       <c r="L204" t="n">
-        <v>4386</v>
+        <v>4373</v>
       </c>
       <c r="M204" t="inlineStr"/>
     </row>
@@ -8836,22 +8836,22 @@
         <v>3.6</v>
       </c>
       <c r="G205" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H205" t="n">
-        <v>90584</v>
+        <v>90429</v>
       </c>
       <c r="I205" t="n">
-        <v>14</v>
+        <v>13.99</v>
       </c>
       <c r="J205" t="n">
-        <v>0.097</v>
+        <v>0.095</v>
       </c>
       <c r="K205" t="n">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="L205" t="n">
-        <v>5512</v>
+        <v>5497</v>
       </c>
       <c r="M205" t="inlineStr"/>
     </row>
@@ -8877,22 +8877,22 @@
         <v>6.1</v>
       </c>
       <c r="G206" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H206" t="n">
-        <v>137591</v>
+        <v>137227</v>
       </c>
       <c r="I206" t="n">
-        <v>22.2</v>
+        <v>22.22</v>
       </c>
       <c r="J206" t="n">
-        <v>0.09</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="K206" t="n">
-        <v>1156</v>
+        <v>1142</v>
       </c>
       <c r="L206" t="n">
-        <v>4191</v>
+        <v>4179</v>
       </c>
       <c r="M206" t="inlineStr"/>
     </row>
@@ -8918,22 +8918,22 @@
         <v>3.8</v>
       </c>
       <c r="G207" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H207" t="n">
-        <v>94972</v>
+        <v>94784</v>
       </c>
       <c r="I207" t="n">
         <v>14.78</v>
       </c>
       <c r="J207" t="n">
-        <v>0.099</v>
+        <v>0.095</v>
       </c>
       <c r="K207" t="n">
-        <v>678</v>
+        <v>674</v>
       </c>
       <c r="L207" t="n">
-        <v>4815</v>
+        <v>4792</v>
       </c>
       <c r="M207" t="inlineStr"/>
     </row>
@@ -8962,19 +8962,19 @@
         <v>0</v>
       </c>
       <c r="H208" t="n">
-        <v>62799</v>
+        <v>62633</v>
       </c>
       <c r="I208" t="n">
-        <v>8.779999999999999</v>
+        <v>8.76</v>
       </c>
       <c r="J208" t="n">
-        <v>0.105</v>
+        <v>0.102</v>
       </c>
       <c r="K208" t="n">
         <v>364</v>
       </c>
       <c r="L208" t="n">
-        <v>5587</v>
+        <v>5568</v>
       </c>
       <c r="M208" t="inlineStr"/>
     </row>
@@ -9003,19 +9003,19 @@
         <v>0</v>
       </c>
       <c r="H209" t="n">
-        <v>112244</v>
+        <v>112104</v>
       </c>
       <c r="I209" t="n">
-        <v>17.24</v>
+        <v>17.29</v>
       </c>
       <c r="J209" t="n">
-        <v>0.094</v>
+        <v>0.091</v>
       </c>
       <c r="K209" t="n">
-        <v>971</v>
+        <v>959</v>
       </c>
       <c r="L209" t="n">
-        <v>4843</v>
+        <v>4832</v>
       </c>
       <c r="M209" t="inlineStr"/>
     </row>
@@ -9044,19 +9044,19 @@
         <v>0</v>
       </c>
       <c r="H210" t="n">
-        <v>70963</v>
+        <v>70837</v>
       </c>
       <c r="I210" t="n">
-        <v>10.16</v>
+        <v>10.17</v>
       </c>
       <c r="J210" t="n">
-        <v>0.102</v>
+        <v>0.1</v>
       </c>
       <c r="K210" t="n">
-        <v>495</v>
+        <v>491</v>
       </c>
       <c r="L210" t="n">
-        <v>5182</v>
+        <v>5168</v>
       </c>
       <c r="M210" t="inlineStr"/>
     </row>
@@ -9085,19 +9085,19 @@
         <v>0</v>
       </c>
       <c r="H211" t="n">
-        <v>42945</v>
+        <v>42849</v>
       </c>
       <c r="I211" t="n">
         <v>4.99</v>
       </c>
       <c r="J211" t="n">
-        <v>0.107</v>
+        <v>0.105</v>
       </c>
       <c r="K211" t="n">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="L211" t="n">
-        <v>5634</v>
+        <v>5619</v>
       </c>
       <c r="M211" t="inlineStr"/>
     </row>
@@ -9123,22 +9123,22 @@
         <v>9.9</v>
       </c>
       <c r="G212" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H212" t="n">
-        <v>195055</v>
+        <v>194812</v>
       </c>
       <c r="I212" t="n">
-        <v>32.39</v>
+        <v>32.37</v>
       </c>
       <c r="J212" t="n">
-        <v>0.077</v>
+        <v>0.075</v>
       </c>
       <c r="K212" t="n">
-        <v>1775</v>
+        <v>1771</v>
       </c>
       <c r="L212" t="n">
-        <v>1419</v>
+        <v>1423</v>
       </c>
       <c r="M212" t="inlineStr"/>
     </row>
@@ -9164,22 +9164,22 @@
         <v>6.7</v>
       </c>
       <c r="G213" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H213" t="n">
-        <v>148044</v>
+        <v>147810</v>
       </c>
       <c r="I213" t="n">
-        <v>24.14</v>
+        <v>24.13</v>
       </c>
       <c r="J213" t="n">
-        <v>0.08699999999999999</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="K213" t="n">
-        <v>1247</v>
+        <v>1240</v>
       </c>
       <c r="L213" t="n">
-        <v>2777</v>
+        <v>2779</v>
       </c>
       <c r="M213" t="inlineStr"/>
     </row>
@@ -9205,22 +9205,22 @@
         <v>4.4</v>
       </c>
       <c r="G214" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H214" t="n">
-        <v>105958</v>
+        <v>105814</v>
       </c>
       <c r="I214" t="n">
         <v>16.53</v>
       </c>
       <c r="J214" t="n">
-        <v>0.096</v>
+        <v>0.093</v>
       </c>
       <c r="K214" t="n">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="L214" t="n">
-        <v>4144</v>
+        <v>4135</v>
       </c>
       <c r="M214" t="inlineStr"/>
     </row>
@@ -9246,22 +9246,22 @@
         <v>6.9</v>
       </c>
       <c r="G215" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H215" t="n">
-        <v>151039</v>
+        <v>150890</v>
       </c>
       <c r="I215" t="n">
-        <v>24.64</v>
+        <v>24.63</v>
       </c>
       <c r="J215" t="n">
-        <v>0.08799999999999999</v>
+        <v>0.08500000000000001</v>
       </c>
       <c r="K215" t="n">
-        <v>1347</v>
+        <v>1344</v>
       </c>
       <c r="L215" t="n">
-        <v>1200</v>
+        <v>1194</v>
       </c>
       <c r="M215" t="inlineStr"/>
     </row>
@@ -9287,22 +9287,22 @@
         <v>4.4</v>
       </c>
       <c r="G216" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H216" t="n">
-        <v>106606</v>
+        <v>106453</v>
       </c>
       <c r="I216" t="n">
         <v>16.86</v>
       </c>
       <c r="J216" t="n">
-        <v>0.096</v>
+        <v>0.093</v>
       </c>
       <c r="K216" t="n">
-        <v>852</v>
+        <v>849</v>
       </c>
       <c r="L216" t="n">
-        <v>2105</v>
+        <v>2092</v>
       </c>
       <c r="M216" t="inlineStr"/>
     </row>
@@ -9331,19 +9331,19 @@
         <v>0</v>
       </c>
       <c r="H217" t="n">
-        <v>70335</v>
+        <v>70226</v>
       </c>
       <c r="I217" t="n">
-        <v>10.25</v>
+        <v>10.23</v>
       </c>
       <c r="J217" t="n">
-        <v>0.103</v>
+        <v>0.1</v>
       </c>
       <c r="K217" t="n">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="L217" t="n">
-        <v>3057</v>
+        <v>3048</v>
       </c>
       <c r="M217" t="inlineStr"/>
     </row>
@@ -9372,19 +9372,19 @@
         <v>0</v>
       </c>
       <c r="H218" t="n">
-        <v>116972</v>
+        <v>116842</v>
       </c>
       <c r="I218" t="n">
-        <v>18.37</v>
+        <v>18.41</v>
       </c>
       <c r="J218" t="n">
-        <v>0.092</v>
+        <v>0.09</v>
       </c>
       <c r="K218" t="n">
-        <v>1055</v>
+        <v>1045</v>
       </c>
       <c r="L218" t="n">
-        <v>1171</v>
+        <v>1162</v>
       </c>
       <c r="M218" t="inlineStr"/>
     </row>
@@ -9413,19 +9413,19 @@
         <v>0</v>
       </c>
       <c r="H219" t="n">
-        <v>74813</v>
+        <v>74715</v>
       </c>
       <c r="I219" t="n">
-        <v>11.11</v>
+        <v>11.12</v>
       </c>
       <c r="J219" t="n">
-        <v>0.101</v>
+        <v>0.099</v>
       </c>
       <c r="K219" t="n">
-        <v>574</v>
+        <v>569</v>
       </c>
       <c r="L219" t="n">
-        <v>1630</v>
+        <v>1623</v>
       </c>
       <c r="M219" t="inlineStr"/>
     </row>
@@ -9454,19 +9454,19 @@
         <v>0</v>
       </c>
       <c r="H220" t="n">
-        <v>44686</v>
+        <v>44593</v>
       </c>
       <c r="I220" t="n">
-        <v>5.6</v>
+        <v>5.61</v>
       </c>
       <c r="J220" t="n">
-        <v>0.107</v>
+        <v>0.105</v>
       </c>
       <c r="K220" t="n">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="L220" t="n">
-        <v>2177</v>
+        <v>2169</v>
       </c>
       <c r="M220" t="inlineStr"/>
     </row>
@@ -9495,19 +9495,19 @@
         <v>0</v>
       </c>
       <c r="H221" t="n">
-        <v>96319</v>
+        <v>96228</v>
       </c>
       <c r="I221" t="n">
-        <v>14.45</v>
+        <v>14.48</v>
       </c>
       <c r="J221" t="n">
-        <v>0.099</v>
+        <v>0.096</v>
       </c>
       <c r="K221" t="n">
-        <v>884</v>
+        <v>876</v>
       </c>
       <c r="L221" t="n">
-        <v>1297</v>
+        <v>1296</v>
       </c>
       <c r="M221" t="inlineStr"/>
     </row>
@@ -9536,19 +9536,19 @@
         <v>0</v>
       </c>
       <c r="H222" t="n">
-        <v>55580</v>
+        <v>55544</v>
       </c>
       <c r="I222" t="n">
-        <v>7.54</v>
+        <v>7.55</v>
       </c>
       <c r="J222" t="n">
-        <v>0.106</v>
+        <v>0.104</v>
       </c>
       <c r="K222" t="n">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="L222" t="n">
-        <v>1484</v>
+        <v>1479</v>
       </c>
       <c r="M222" t="inlineStr"/>
     </row>
@@ -9577,19 +9577,19 @@
         <v>0</v>
       </c>
       <c r="H223" t="n">
-        <v>30124</v>
+        <v>30027</v>
       </c>
       <c r="I223" t="n">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="J223" t="n">
-        <v>0.112</v>
+        <v>0.109</v>
       </c>
       <c r="K223" t="n">
         <v>135</v>
       </c>
       <c r="L223" t="n">
-        <v>1724</v>
+        <v>1719</v>
       </c>
       <c r="M223" t="inlineStr"/>
     </row>
@@ -9618,19 +9618,19 @@
         <v>0</v>
       </c>
       <c r="H224" t="n">
-        <v>87188</v>
+        <v>87100</v>
       </c>
       <c r="I224" t="n">
-        <v>12.61</v>
+        <v>12.64</v>
       </c>
       <c r="J224" t="n">
-        <v>0.101</v>
+        <v>0.098</v>
       </c>
       <c r="K224" t="n">
-        <v>809</v>
+        <v>801</v>
       </c>
       <c r="L224" t="n">
-        <v>1437</v>
+        <v>1436</v>
       </c>
       <c r="M224" t="inlineStr"/>
     </row>
@@ -9659,19 +9659,19 @@
         <v>0</v>
       </c>
       <c r="H225" t="n">
-        <v>47112</v>
+        <v>47007</v>
       </c>
       <c r="I225" t="n">
-        <v>5.87</v>
+        <v>5.86</v>
       </c>
       <c r="J225" t="n">
-        <v>0.108</v>
+        <v>0.106</v>
       </c>
       <c r="K225" t="n">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="L225" t="n">
-        <v>1495</v>
+        <v>1492</v>
       </c>
       <c r="M225" t="inlineStr"/>
     </row>
@@ -9700,19 +9700,19 @@
         <v>0</v>
       </c>
       <c r="H226" t="n">
-        <v>23879</v>
+        <v>23809</v>
       </c>
       <c r="I226" t="n">
-        <v>1.7</v>
+        <v>1.68</v>
       </c>
       <c r="J226" t="n">
-        <v>0.114</v>
+        <v>0.111</v>
       </c>
       <c r="K226" t="n">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="L226" t="n">
-        <v>1579</v>
+        <v>1573</v>
       </c>
       <c r="M226" t="inlineStr"/>
     </row>
@@ -9738,22 +9738,22 @@
         <v>8.300000000000001</v>
       </c>
       <c r="G227" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H227" t="n">
-        <v>173797</v>
+        <v>173707</v>
       </c>
       <c r="I227" t="n">
-        <v>28.02</v>
+        <v>28.04</v>
       </c>
       <c r="J227" t="n">
-        <v>0.083</v>
+        <v>0.081</v>
       </c>
       <c r="K227" t="n">
-        <v>1655</v>
+        <v>1651</v>
       </c>
       <c r="L227" t="n">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="M227" t="inlineStr"/>
     </row>
@@ -9782,19 +9782,19 @@
         <v>0</v>
       </c>
       <c r="H228" t="n">
-        <v>126984</v>
+        <v>126894</v>
       </c>
       <c r="I228" t="n">
         <v>19.93</v>
       </c>
       <c r="J228" t="n">
-        <v>0.092</v>
+        <v>0.089</v>
       </c>
       <c r="K228" t="n">
-        <v>1113</v>
+        <v>1110</v>
       </c>
       <c r="L228" t="n">
-        <v>2399</v>
+        <v>2401</v>
       </c>
       <c r="M228" t="inlineStr"/>
     </row>
@@ -9823,19 +9823,19 @@
         <v>0</v>
       </c>
       <c r="H229" t="n">
-        <v>85609</v>
+        <v>85630</v>
       </c>
       <c r="I229" t="n">
-        <v>12.53</v>
+        <v>12.55</v>
       </c>
       <c r="J229" t="n">
-        <v>0.099</v>
+        <v>0.097</v>
       </c>
       <c r="K229" t="n">
         <v>666</v>
       </c>
       <c r="L229" t="n">
-        <v>3640</v>
+        <v>3627</v>
       </c>
       <c r="M229" t="inlineStr"/>
     </row>
@@ -9861,22 +9861,22 @@
         <v>5.7</v>
       </c>
       <c r="G230" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H230" t="n">
-        <v>130674</v>
+        <v>130571</v>
       </c>
       <c r="I230" t="n">
-        <v>20.55</v>
+        <v>20.57</v>
       </c>
       <c r="J230" t="n">
-        <v>0.091</v>
+        <v>0.08799999999999999</v>
       </c>
       <c r="K230" t="n">
-        <v>1222</v>
+        <v>1215</v>
       </c>
       <c r="L230" t="n">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="M230" t="inlineStr"/>
     </row>
@@ -9905,19 +9905,19 @@
         <v>0</v>
       </c>
       <c r="H231" t="n">
-        <v>86759</v>
+        <v>86735</v>
       </c>
       <c r="I231" t="n">
-        <v>12.99</v>
+        <v>13.01</v>
       </c>
       <c r="J231" t="n">
-        <v>0.101</v>
+        <v>0.097</v>
       </c>
       <c r="K231" t="n">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="L231" t="n">
-        <v>1386</v>
+        <v>1376</v>
       </c>
       <c r="M231" t="inlineStr"/>
     </row>
@@ -9946,19 +9946,19 @@
         <v>0</v>
       </c>
       <c r="H232" t="n">
-        <v>52113</v>
+        <v>52153</v>
       </c>
       <c r="I232" t="n">
-        <v>6.74</v>
+        <v>6.76</v>
       </c>
       <c r="J232" t="n">
-        <v>0.108</v>
+        <v>0.104</v>
       </c>
       <c r="K232" t="n">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="L232" t="n">
-        <v>2149</v>
+        <v>2138</v>
       </c>
       <c r="M232" t="inlineStr"/>
     </row>
@@ -9987,19 +9987,19 @@
         <v>0</v>
       </c>
       <c r="H233" t="n">
-        <v>99787</v>
+        <v>99790</v>
       </c>
       <c r="I233" t="n">
-        <v>15.02</v>
+        <v>15.07</v>
       </c>
       <c r="J233" t="n">
-        <v>0.098</v>
+        <v>0.096</v>
       </c>
       <c r="K233" t="n">
-        <v>932</v>
+        <v>926</v>
       </c>
       <c r="L233" t="n">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="M233" t="inlineStr"/>
     </row>
@@ -10028,19 +10028,19 @@
         <v>0</v>
       </c>
       <c r="H234" t="n">
-        <v>58352</v>
+        <v>58354</v>
       </c>
       <c r="I234" t="n">
-        <v>7.95</v>
+        <v>7.98</v>
       </c>
       <c r="J234" t="n">
-        <v>0.106</v>
+        <v>0.104</v>
       </c>
       <c r="K234" t="n">
-        <v>453</v>
+        <v>450</v>
       </c>
       <c r="L234" t="n">
-        <v>573</v>
+        <v>571</v>
       </c>
       <c r="M234" t="inlineStr"/>
     </row>
@@ -10069,16 +10069,16 @@
         <v>0</v>
       </c>
       <c r="H235" t="n">
-        <v>30885</v>
+        <v>30889</v>
       </c>
       <c r="I235" t="n">
         <v>3.04</v>
       </c>
       <c r="J235" t="n">
-        <v>0.112</v>
+        <v>0.109</v>
       </c>
       <c r="K235" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="L235" t="n">
         <v>890</v>
@@ -10110,19 +10110,19 @@
         <v>0</v>
       </c>
       <c r="H236" t="n">
-        <v>85786</v>
+        <v>85820</v>
       </c>
       <c r="I236" t="n">
-        <v>12.39</v>
+        <v>12.44</v>
       </c>
       <c r="J236" t="n">
-        <v>0.102</v>
+        <v>0.099</v>
       </c>
       <c r="K236" t="n">
-        <v>807</v>
+        <v>802</v>
       </c>
       <c r="L236" t="n">
-        <v>137</v>
+        <v>142</v>
       </c>
       <c r="M236" t="inlineStr"/>
     </row>
@@ -10151,19 +10151,19 @@
         <v>0</v>
       </c>
       <c r="H237" t="n">
-        <v>45631</v>
+        <v>45627</v>
       </c>
       <c r="I237" t="n">
-        <v>5.64</v>
+        <v>5.66</v>
       </c>
       <c r="J237" t="n">
-        <v>0.109</v>
+        <v>0.107</v>
       </c>
       <c r="K237" t="n">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="L237" t="n">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="M237" t="inlineStr"/>
     </row>
@@ -10192,19 +10192,19 @@
         <v>0</v>
       </c>
       <c r="H238" t="n">
-        <v>22407</v>
+        <v>22417</v>
       </c>
       <c r="I238" t="n">
         <v>1.49</v>
       </c>
       <c r="J238" t="n">
-        <v>0.114</v>
+        <v>0.111</v>
       </c>
       <c r="K238" t="n">
         <v>75</v>
       </c>
       <c r="L238" t="n">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="M238" t="inlineStr"/>
     </row>
@@ -10227,25 +10227,25 @@
         <v>70</v>
       </c>
       <c r="F239" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="G239" t="n">
         <v>0</v>
       </c>
       <c r="H239" t="n">
-        <v>83222</v>
+        <v>83252</v>
       </c>
       <c r="I239" t="n">
-        <v>11.8</v>
+        <v>11.84</v>
       </c>
       <c r="J239" t="n">
-        <v>0.103</v>
+        <v>0.1</v>
       </c>
       <c r="K239" t="n">
-        <v>780</v>
+        <v>774</v>
       </c>
       <c r="L239" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="M239" t="inlineStr"/>
     </row>
@@ -10274,19 +10274,19 @@
         <v>0</v>
       </c>
       <c r="H240" t="n">
-        <v>43384</v>
+        <v>43371</v>
       </c>
       <c r="I240" t="n">
-        <v>5.13</v>
+        <v>5.14</v>
       </c>
       <c r="J240" t="n">
-        <v>0.109</v>
+        <v>0.108</v>
       </c>
       <c r="K240" t="n">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="L240" t="n">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="M240" t="inlineStr"/>
     </row>
@@ -10315,19 +10315,19 @@
         <v>0</v>
       </c>
       <c r="H241" t="n">
-        <v>21202</v>
+        <v>21175</v>
       </c>
       <c r="I241" t="n">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="J241" t="n">
-        <v>0.115</v>
+        <v>0.112</v>
       </c>
       <c r="K241" t="n">
         <v>59</v>
       </c>
       <c r="L241" t="n">
-        <v>129</v>
+        <v>134</v>
       </c>
       <c r="M241" t="inlineStr">
         <is>
@@ -10357,22 +10357,22 @@
         <v>8.199999999999999</v>
       </c>
       <c r="G242" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H242" t="n">
-        <v>172970</v>
+        <v>172837</v>
       </c>
       <c r="I242" t="n">
-        <v>27.65</v>
+        <v>27.67</v>
       </c>
       <c r="J242" t="n">
-        <v>0.083</v>
+        <v>0.082</v>
       </c>
       <c r="K242" t="n">
-        <v>1647</v>
+        <v>1643</v>
       </c>
       <c r="L242" t="n">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="M242" t="inlineStr"/>
     </row>
@@ -10398,22 +10398,22 @@
         <v>5.4</v>
       </c>
       <c r="G243" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H243" t="n">
-        <v>126146</v>
+        <v>126055</v>
       </c>
       <c r="I243" t="n">
-        <v>19.57</v>
+        <v>19.58</v>
       </c>
       <c r="J243" t="n">
-        <v>0.092</v>
+        <v>0.09</v>
       </c>
       <c r="K243" t="n">
-        <v>1104</v>
+        <v>1101</v>
       </c>
       <c r="L243" t="n">
-        <v>2369</v>
+        <v>2368</v>
       </c>
       <c r="M243" t="inlineStr"/>
     </row>
@@ -10442,19 +10442,19 @@
         <v>0</v>
       </c>
       <c r="H244" t="n">
-        <v>84880</v>
+        <v>84866</v>
       </c>
       <c r="I244" t="n">
-        <v>12.2</v>
+        <v>12.22</v>
       </c>
       <c r="J244" t="n">
-        <v>0.099</v>
+        <v>0.098</v>
       </c>
       <c r="K244" t="n">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="L244" t="n">
-        <v>3597</v>
+        <v>3584</v>
       </c>
       <c r="M244" t="inlineStr"/>
     </row>
@@ -10480,22 +10480,22 @@
         <v>5.6</v>
       </c>
       <c r="G245" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H245" t="n">
-        <v>129944</v>
+        <v>129814</v>
       </c>
       <c r="I245" t="n">
-        <v>20.21</v>
+        <v>20.24</v>
       </c>
       <c r="J245" t="n">
-        <v>0.092</v>
+        <v>0.089</v>
       </c>
       <c r="K245" t="n">
-        <v>1212</v>
+        <v>1205</v>
       </c>
       <c r="L245" t="n">
-        <v>587</v>
+        <v>585</v>
       </c>
       <c r="M245" t="inlineStr"/>
     </row>
@@ -10524,19 +10524,19 @@
         <v>0</v>
       </c>
       <c r="H246" t="n">
-        <v>86071</v>
+        <v>85991</v>
       </c>
       <c r="I246" t="n">
-        <v>12.67</v>
+        <v>12.68</v>
       </c>
       <c r="J246" t="n">
-        <v>0.101</v>
+        <v>0.098</v>
       </c>
       <c r="K246" t="n">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="L246" t="n">
-        <v>1327</v>
+        <v>1315</v>
       </c>
       <c r="M246" t="inlineStr"/>
     </row>
@@ -10565,19 +10565,19 @@
         <v>0</v>
       </c>
       <c r="H247" t="n">
-        <v>51592</v>
+        <v>51538</v>
       </c>
       <c r="I247" t="n">
         <v>6.46</v>
       </c>
       <c r="J247" t="n">
-        <v>0.108</v>
+        <v>0.105</v>
       </c>
       <c r="K247" t="n">
         <v>341</v>
       </c>
       <c r="L247" t="n">
-        <v>2075</v>
+        <v>2063</v>
       </c>
       <c r="M247" t="inlineStr"/>
     </row>
@@ -10606,19 +10606,19 @@
         <v>0</v>
       </c>
       <c r="H248" t="n">
-        <v>99314</v>
+        <v>99254</v>
       </c>
       <c r="I248" t="n">
-        <v>14.76</v>
+        <v>14.78</v>
       </c>
       <c r="J248" t="n">
-        <v>0.099</v>
+        <v>0.096</v>
       </c>
       <c r="K248" t="n">
-        <v>921</v>
+        <v>916</v>
       </c>
       <c r="L248" t="n">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="M248" t="inlineStr"/>
     </row>
@@ -10647,19 +10647,19 @@
         <v>0</v>
       </c>
       <c r="H249" t="n">
-        <v>57920</v>
+        <v>57882</v>
       </c>
       <c r="I249" t="n">
-        <v>7.69</v>
+        <v>7.71</v>
       </c>
       <c r="J249" t="n">
-        <v>0.106</v>
+        <v>0.104</v>
       </c>
       <c r="K249" t="n">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="L249" t="n">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="M249" t="inlineStr"/>
     </row>
@@ -10688,19 +10688,19 @@
         <v>0</v>
       </c>
       <c r="H250" t="n">
-        <v>30648</v>
+        <v>30637</v>
       </c>
       <c r="I250" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="J250" t="n">
-        <v>0.112</v>
+        <v>0.109</v>
       </c>
       <c r="K250" t="n">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="L250" t="n">
-        <v>784</v>
+        <v>778</v>
       </c>
       <c r="M250" t="inlineStr"/>
     </row>
@@ -10729,19 +10729,19 @@
         <v>0</v>
       </c>
       <c r="H251" t="n">
-        <v>85924</v>
+        <v>85943</v>
       </c>
       <c r="I251" t="n">
-        <v>12.24</v>
+        <v>12.28</v>
       </c>
       <c r="J251" t="n">
-        <v>0.102</v>
+        <v>0.099</v>
       </c>
       <c r="K251" t="n">
-        <v>801</v>
+        <v>796</v>
       </c>
       <c r="L251" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="M251" t="inlineStr"/>
     </row>
@@ -10770,16 +10770,16 @@
         <v>0</v>
       </c>
       <c r="H252" t="n">
-        <v>45803</v>
+        <v>45793</v>
       </c>
       <c r="I252" t="n">
-        <v>5.51</v>
+        <v>5.52</v>
       </c>
       <c r="J252" t="n">
-        <v>0.109</v>
+        <v>0.107</v>
       </c>
       <c r="K252" t="n">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="L252" t="n">
         <v>85</v>
@@ -10811,13 +10811,13 @@
         <v>0</v>
       </c>
       <c r="H253" t="n">
-        <v>22818</v>
+        <v>22786</v>
       </c>
       <c r="I253" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="J253" t="n">
-        <v>0.115</v>
+        <v>0.111</v>
       </c>
       <c r="K253" t="n">
         <v>71</v>
@@ -10852,19 +10852,19 @@
         <v>0</v>
       </c>
       <c r="H254" t="n">
-        <v>83950</v>
+        <v>83962</v>
       </c>
       <c r="I254" t="n">
-        <v>11.76</v>
+        <v>11.8</v>
       </c>
       <c r="J254" t="n">
-        <v>0.103</v>
+        <v>0.1</v>
       </c>
       <c r="K254" t="n">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="L254" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M254" t="inlineStr"/>
     </row>
@@ -10893,19 +10893,19 @@
         <v>0</v>
       </c>
       <c r="H255" t="n">
-        <v>44126</v>
+        <v>44092</v>
       </c>
       <c r="I255" t="n">
         <v>5.1</v>
       </c>
       <c r="J255" t="n">
-        <v>0.109</v>
+        <v>0.108</v>
       </c>
       <c r="K255" t="n">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="L255" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="M255" t="inlineStr"/>
     </row>
@@ -10934,19 +10934,19 @@
         <v>0</v>
       </c>
       <c r="H256" t="n">
-        <v>22001</v>
+        <v>21962</v>
       </c>
       <c r="I256" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="J256" t="n">
-        <v>0.115</v>
+        <v>0.112</v>
       </c>
       <c r="K256" t="n">
         <v>58</v>
       </c>
       <c r="L256" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="M256" t="inlineStr"/>
     </row>
@@ -10972,22 +10972,22 @@
         <v>8.300000000000001</v>
       </c>
       <c r="G257" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H257" t="n">
-        <v>173933</v>
+        <v>173788</v>
       </c>
       <c r="I257" t="n">
-        <v>27.65</v>
+        <v>27.66</v>
       </c>
       <c r="J257" t="n">
-        <v>0.083</v>
+        <v>0.082</v>
       </c>
       <c r="K257" t="n">
-        <v>1647</v>
+        <v>1643</v>
       </c>
       <c r="L257" t="n">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="M257" t="inlineStr"/>
     </row>
@@ -11013,22 +11013,22 @@
         <v>5.4</v>
       </c>
       <c r="G258" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H258" t="n">
-        <v>127109</v>
+        <v>127006</v>
       </c>
       <c r="I258" t="n">
-        <v>19.56</v>
+        <v>19.57</v>
       </c>
       <c r="J258" t="n">
-        <v>0.092</v>
+        <v>0.09</v>
       </c>
       <c r="K258" t="n">
-        <v>1103</v>
+        <v>1100</v>
       </c>
       <c r="L258" t="n">
-        <v>2368</v>
+        <v>2367</v>
       </c>
       <c r="M258" t="inlineStr"/>
     </row>
@@ -11057,19 +11057,19 @@
         <v>0</v>
       </c>
       <c r="H259" t="n">
-        <v>85847</v>
+        <v>85818</v>
       </c>
       <c r="I259" t="n">
-        <v>12.2</v>
+        <v>12.21</v>
       </c>
       <c r="J259" t="n">
-        <v>0.099</v>
+        <v>0.098</v>
       </c>
       <c r="K259" t="n">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="L259" t="n">
-        <v>3596</v>
+        <v>3583</v>
       </c>
       <c r="M259" t="inlineStr"/>
     </row>
@@ -11095,22 +11095,22 @@
         <v>5.6</v>
       </c>
       <c r="G260" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="H260" t="n">
-        <v>130915</v>
+        <v>130769</v>
       </c>
       <c r="I260" t="n">
-        <v>20.21</v>
+        <v>20.23</v>
       </c>
       <c r="J260" t="n">
-        <v>0.092</v>
+        <v>0.089</v>
       </c>
       <c r="K260" t="n">
-        <v>1212</v>
+        <v>1205</v>
       </c>
       <c r="L260" t="n">
-        <v>587</v>
+        <v>584</v>
       </c>
       <c r="M260" t="inlineStr"/>
     </row>
@@ -11139,19 +11139,19 @@
         <v>0</v>
       </c>
       <c r="H261" t="n">
-        <v>87041</v>
+        <v>86947</v>
       </c>
       <c r="I261" t="n">
-        <v>12.66</v>
+        <v>12.67</v>
       </c>
       <c r="J261" t="n">
-        <v>0.101</v>
+        <v>0.098</v>
       </c>
       <c r="K261" t="n">
-        <v>706</v>
+        <v>703</v>
       </c>
       <c r="L261" t="n">
-        <v>1327</v>
+        <v>1315</v>
       </c>
       <c r="M261" t="inlineStr"/>
     </row>
@@ -11180,19 +11180,19 @@
         <v>0</v>
       </c>
       <c r="H262" t="n">
-        <v>52562</v>
+        <v>52494</v>
       </c>
       <c r="I262" t="n">
-        <v>6.46</v>
+        <v>6.45</v>
       </c>
       <c r="J262" t="n">
-        <v>0.108</v>
+        <v>0.105</v>
       </c>
       <c r="K262" t="n">
         <v>341</v>
       </c>
       <c r="L262" t="n">
-        <v>2074</v>
+        <v>2062</v>
       </c>
       <c r="M262" t="inlineStr"/>
     </row>
@@ -11221,19 +11221,19 @@
         <v>0</v>
       </c>
       <c r="H263" t="n">
-        <v>100286</v>
+        <v>100207</v>
       </c>
       <c r="I263" t="n">
-        <v>14.76</v>
+        <v>14.78</v>
       </c>
       <c r="J263" t="n">
-        <v>0.099</v>
+        <v>0.096</v>
       </c>
       <c r="K263" t="n">
-        <v>922</v>
+        <v>916</v>
       </c>
       <c r="L263" t="n">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="M263" t="inlineStr"/>
     </row>
@@ -11262,19 +11262,19 @@
         <v>0</v>
       </c>
       <c r="H264" t="n">
-        <v>58888</v>
+        <v>58837</v>
       </c>
       <c r="I264" t="n">
-        <v>7.69</v>
+        <v>7.71</v>
       </c>
       <c r="J264" t="n">
-        <v>0.106</v>
+        <v>0.104</v>
       </c>
       <c r="K264" t="n">
-        <v>443</v>
+        <v>440</v>
       </c>
       <c r="L264" t="n">
-        <v>485</v>
+        <v>478</v>
       </c>
       <c r="M264" t="inlineStr"/>
     </row>
@@ -11303,19 +11303,19 @@
         <v>0</v>
       </c>
       <c r="H265" t="n">
-        <v>31616</v>
+        <v>31595</v>
       </c>
       <c r="I265" t="n">
-        <v>2.83</v>
+        <v>2.82</v>
       </c>
       <c r="J265" t="n">
-        <v>0.112</v>
+        <v>0.109</v>
       </c>
       <c r="K265" t="n">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="L265" t="n">
-        <v>783</v>
+        <v>776</v>
       </c>
       <c r="M265" t="inlineStr"/>
     </row>
@@ -11344,16 +11344,16 @@
         <v>0</v>
       </c>
       <c r="H266" t="n">
-        <v>86894</v>
+        <v>86904</v>
       </c>
       <c r="I266" t="n">
-        <v>12.24</v>
+        <v>12.28</v>
       </c>
       <c r="J266" t="n">
-        <v>0.102</v>
+        <v>0.099</v>
       </c>
       <c r="K266" t="n">
-        <v>801</v>
+        <v>796</v>
       </c>
       <c r="L266" t="n">
         <v>36</v>
@@ -11385,19 +11385,19 @@
         <v>0</v>
       </c>
       <c r="H267" t="n">
-        <v>46772</v>
+        <v>46757</v>
       </c>
       <c r="I267" t="n">
-        <v>5.51</v>
+        <v>5.52</v>
       </c>
       <c r="J267" t="n">
-        <v>0.109</v>
+        <v>0.107</v>
       </c>
       <c r="K267" t="n">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="L267" t="n">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="M267" t="inlineStr"/>
     </row>
@@ -11426,19 +11426,19 @@
         <v>0</v>
       </c>
       <c r="H268" t="n">
-        <v>23788</v>
+        <v>23754</v>
       </c>
       <c r="I268" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="J268" t="n">
-        <v>0.115</v>
+        <v>0.111</v>
       </c>
       <c r="K268" t="n">
         <v>71</v>
       </c>
       <c r="L268" t="n">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="M268" t="inlineStr"/>
     </row>
@@ -11467,16 +11467,16 @@
         <v>0</v>
       </c>
       <c r="H269" t="n">
-        <v>84925</v>
+        <v>84940</v>
       </c>
       <c r="I269" t="n">
-        <v>11.76</v>
+        <v>11.8</v>
       </c>
       <c r="J269" t="n">
-        <v>0.103</v>
+        <v>0.1</v>
       </c>
       <c r="K269" t="n">
-        <v>778</v>
+        <v>773</v>
       </c>
       <c r="L269" t="n">
         <v>3</v>
@@ -11508,19 +11508,19 @@
         <v>0</v>
       </c>
       <c r="H270" t="n">
-        <v>45101</v>
+        <v>45070</v>
       </c>
       <c r="I270" t="n">
         <v>5.1</v>
       </c>
       <c r="J270" t="n">
-        <v>0.109</v>
+        <v>0.108</v>
       </c>
       <c r="K270" t="n">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="L270" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M270" t="inlineStr"/>
     </row>
@@ -11549,19 +11549,19 @@
         <v>0</v>
       </c>
       <c r="H271" t="n">
-        <v>22979</v>
+        <v>22943</v>
       </c>
       <c r="I271" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="J271" t="n">
-        <v>0.115</v>
+        <v>0.112</v>
       </c>
       <c r="K271" t="n">
         <v>58</v>
       </c>
       <c r="L271" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="M271" t="inlineStr"/>
     </row>
